--- a/output/version3/test/20-15/MARL/IL/RL-RL with pt (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-15/MARL/IL/RL-RL with pt (+comm)/(RL+RL) test results.xlsx
@@ -474,34 +474,34 @@
         <v>842</v>
       </c>
       <c r="C2" t="n">
-        <v>737</v>
+        <v>766</v>
       </c>
       <c r="D2" t="n">
-        <v>805</v>
+        <v>845</v>
       </c>
       <c r="E2" t="n">
-        <v>841</v>
+        <v>952</v>
       </c>
       <c r="F2" t="n">
-        <v>818</v>
+        <v>774</v>
       </c>
       <c r="G2" t="n">
-        <v>850</v>
+        <v>936</v>
       </c>
       <c r="H2" t="n">
+        <v>907</v>
+      </c>
+      <c r="I2" t="n">
         <v>958</v>
       </c>
-      <c r="I2" t="n">
-        <v>804</v>
-      </c>
       <c r="J2" t="n">
-        <v>927</v>
+        <v>860</v>
       </c>
       <c r="K2" t="n">
-        <v>805</v>
+        <v>1034</v>
       </c>
       <c r="L2" t="n">
-        <v>838.7</v>
+        <v>887.4</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>870</v>
+        <v>851</v>
       </c>
       <c r="C3" t="n">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="D3" t="n">
-        <v>831</v>
+        <v>956</v>
       </c>
       <c r="E3" t="n">
-        <v>962</v>
+        <v>889</v>
       </c>
       <c r="F3" t="n">
-        <v>970</v>
+        <v>854</v>
       </c>
       <c r="G3" t="n">
-        <v>821</v>
+        <v>918</v>
       </c>
       <c r="H3" t="n">
-        <v>1068</v>
+        <v>901</v>
       </c>
       <c r="I3" t="n">
-        <v>809</v>
+        <v>1014</v>
       </c>
       <c r="J3" t="n">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="K3" t="n">
-        <v>1123</v>
+        <v>1047</v>
       </c>
       <c r="L3" t="n">
-        <v>920.9</v>
+        <v>918.5</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>882</v>
+        <v>943</v>
       </c>
       <c r="C4" t="n">
-        <v>809</v>
+        <v>766</v>
       </c>
       <c r="D4" t="n">
-        <v>1015</v>
+        <v>973</v>
       </c>
       <c r="E4" t="n">
-        <v>831</v>
+        <v>796</v>
       </c>
       <c r="F4" t="n">
-        <v>916</v>
+        <v>865</v>
       </c>
       <c r="G4" t="n">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="H4" t="n">
-        <v>799</v>
+        <v>880</v>
       </c>
       <c r="I4" t="n">
-        <v>818</v>
+        <v>941</v>
       </c>
       <c r="J4" t="n">
-        <v>933</v>
+        <v>730</v>
       </c>
       <c r="K4" t="n">
-        <v>763</v>
+        <v>842</v>
       </c>
       <c r="L4" t="n">
-        <v>856.4</v>
+        <v>854</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>786</v>
+        <v>878</v>
       </c>
       <c r="C5" t="n">
-        <v>758</v>
+        <v>841</v>
       </c>
       <c r="D5" t="n">
-        <v>837</v>
+        <v>785</v>
       </c>
       <c r="E5" t="n">
-        <v>796</v>
+        <v>817</v>
       </c>
       <c r="F5" t="n">
-        <v>851</v>
+        <v>941</v>
       </c>
       <c r="G5" t="n">
-        <v>717</v>
+        <v>903</v>
       </c>
       <c r="H5" t="n">
-        <v>783</v>
+        <v>864</v>
       </c>
       <c r="I5" t="n">
-        <v>1012</v>
+        <v>825</v>
       </c>
       <c r="J5" t="n">
-        <v>873</v>
+        <v>838</v>
       </c>
       <c r="K5" t="n">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="L5" t="n">
-        <v>815.6</v>
+        <v>842.9</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="C6" t="n">
-        <v>686</v>
+        <v>740</v>
       </c>
       <c r="D6" t="n">
-        <v>704</v>
+        <v>687</v>
       </c>
       <c r="E6" t="n">
-        <v>818</v>
+        <v>658</v>
       </c>
       <c r="F6" t="n">
-        <v>662</v>
+        <v>850</v>
       </c>
       <c r="G6" t="n">
-        <v>667</v>
+        <v>731</v>
       </c>
       <c r="H6" t="n">
-        <v>899</v>
+        <v>633</v>
       </c>
       <c r="I6" t="n">
-        <v>821</v>
+        <v>697</v>
       </c>
       <c r="J6" t="n">
-        <v>666</v>
+        <v>722</v>
       </c>
       <c r="K6" t="n">
-        <v>602</v>
+        <v>822</v>
       </c>
       <c r="L6" t="n">
-        <v>722.5</v>
+        <v>725.1</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>761</v>
+        <v>751</v>
       </c>
       <c r="C7" t="n">
-        <v>932</v>
+        <v>870</v>
       </c>
       <c r="D7" t="n">
-        <v>952</v>
+        <v>770</v>
       </c>
       <c r="E7" t="n">
-        <v>814</v>
+        <v>837</v>
       </c>
       <c r="F7" t="n">
-        <v>855</v>
+        <v>819</v>
       </c>
       <c r="G7" t="n">
-        <v>738</v>
+        <v>1002</v>
       </c>
       <c r="H7" t="n">
-        <v>875</v>
+        <v>821</v>
       </c>
       <c r="I7" t="n">
-        <v>815</v>
+        <v>838</v>
       </c>
       <c r="J7" t="n">
-        <v>885</v>
+        <v>842</v>
       </c>
       <c r="K7" t="n">
-        <v>808</v>
+        <v>862</v>
       </c>
       <c r="L7" t="n">
-        <v>843.5</v>
+        <v>841.2</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>909</v>
+        <v>776</v>
       </c>
       <c r="C8" t="n">
-        <v>948</v>
+        <v>846</v>
       </c>
       <c r="D8" t="n">
-        <v>813</v>
+        <v>824</v>
       </c>
       <c r="E8" t="n">
-        <v>847</v>
+        <v>757</v>
       </c>
       <c r="F8" t="n">
-        <v>810</v>
+        <v>838</v>
       </c>
       <c r="G8" t="n">
-        <v>745</v>
+        <v>870</v>
       </c>
       <c r="H8" t="n">
-        <v>773</v>
+        <v>834</v>
       </c>
       <c r="I8" t="n">
-        <v>833</v>
+        <v>765</v>
       </c>
       <c r="J8" t="n">
-        <v>846</v>
+        <v>800</v>
       </c>
       <c r="K8" t="n">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="L8" t="n">
-        <v>850.4</v>
+        <v>828.3</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>899</v>
+        <v>850</v>
       </c>
       <c r="C9" t="n">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D9" t="n">
-        <v>843</v>
+        <v>791</v>
       </c>
       <c r="E9" t="n">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="F9" t="n">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="G9" t="n">
-        <v>845</v>
+        <v>1038</v>
       </c>
       <c r="H9" t="n">
-        <v>900</v>
+        <v>853</v>
       </c>
       <c r="I9" t="n">
-        <v>848</v>
+        <v>731</v>
       </c>
       <c r="J9" t="n">
-        <v>1002</v>
+        <v>924</v>
       </c>
       <c r="K9" t="n">
-        <v>948</v>
+        <v>754</v>
       </c>
       <c r="L9" t="n">
-        <v>880.2</v>
+        <v>844.4</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>961</v>
+        <v>933</v>
       </c>
       <c r="C10" t="n">
-        <v>797</v>
+        <v>952</v>
       </c>
       <c r="D10" t="n">
-        <v>760</v>
+        <v>786</v>
       </c>
       <c r="E10" t="n">
-        <v>778</v>
+        <v>939</v>
       </c>
       <c r="F10" t="n">
-        <v>888</v>
+        <v>816</v>
       </c>
       <c r="G10" t="n">
-        <v>823</v>
+        <v>951</v>
       </c>
       <c r="H10" t="n">
-        <v>765</v>
+        <v>865</v>
       </c>
       <c r="I10" t="n">
-        <v>875</v>
+        <v>754</v>
       </c>
       <c r="J10" t="n">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="K10" t="n">
-        <v>940</v>
+        <v>918</v>
       </c>
       <c r="L10" t="n">
-        <v>842.8</v>
+        <v>875.1</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>908</v>
+        <v>742</v>
       </c>
       <c r="C11" t="n">
-        <v>812</v>
+        <v>834</v>
       </c>
       <c r="D11" t="n">
+        <v>768</v>
+      </c>
+      <c r="E11" t="n">
         <v>836</v>
       </c>
-      <c r="E11" t="n">
-        <v>800</v>
-      </c>
       <c r="F11" t="n">
-        <v>899</v>
+        <v>779</v>
       </c>
       <c r="G11" t="n">
-        <v>814</v>
+        <v>943</v>
       </c>
       <c r="H11" t="n">
-        <v>849</v>
+        <v>748</v>
       </c>
       <c r="I11" t="n">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="J11" t="n">
-        <v>848</v>
+        <v>869</v>
       </c>
       <c r="K11" t="n">
-        <v>770</v>
+        <v>813</v>
       </c>
       <c r="L11" t="n">
-        <v>838.3</v>
+        <v>825.2</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>781</v>
+        <v>1092</v>
       </c>
       <c r="C12" t="n">
-        <v>859</v>
+        <v>1005</v>
       </c>
       <c r="D12" t="n">
-        <v>889</v>
+        <v>817</v>
       </c>
       <c r="E12" t="n">
-        <v>708</v>
+        <v>843</v>
       </c>
       <c r="F12" t="n">
-        <v>1014</v>
+        <v>732</v>
       </c>
       <c r="G12" t="n">
-        <v>933</v>
+        <v>1039</v>
       </c>
       <c r="H12" t="n">
-        <v>871</v>
+        <v>860</v>
       </c>
       <c r="I12" t="n">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="J12" t="n">
-        <v>860</v>
+        <v>932</v>
       </c>
       <c r="K12" t="n">
-        <v>1017</v>
+        <v>881</v>
       </c>
       <c r="L12" t="n">
-        <v>877.5</v>
+        <v>903.1</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C13" t="n">
-        <v>682</v>
+        <v>922</v>
       </c>
       <c r="D13" t="n">
-        <v>748</v>
+        <v>771</v>
       </c>
       <c r="E13" t="n">
-        <v>709</v>
+        <v>908</v>
       </c>
       <c r="F13" t="n">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="G13" t="n">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="H13" t="n">
-        <v>684</v>
+        <v>712</v>
       </c>
       <c r="I13" t="n">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="J13" t="n">
-        <v>873</v>
+        <v>760</v>
       </c>
       <c r="K13" t="n">
-        <v>786</v>
+        <v>751</v>
       </c>
       <c r="L13" t="n">
-        <v>735.8</v>
+        <v>767.1</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>1005</v>
+        <v>770</v>
       </c>
       <c r="C14" t="n">
-        <v>849</v>
+        <v>756</v>
       </c>
       <c r="D14" t="n">
-        <v>880</v>
+        <v>809</v>
       </c>
       <c r="E14" t="n">
-        <v>705</v>
+        <v>789</v>
       </c>
       <c r="F14" t="n">
-        <v>754</v>
+        <v>780</v>
       </c>
       <c r="G14" t="n">
-        <v>774</v>
+        <v>790</v>
       </c>
       <c r="H14" t="n">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="I14" t="n">
-        <v>833</v>
+        <v>922</v>
       </c>
       <c r="J14" t="n">
-        <v>769</v>
+        <v>778</v>
       </c>
       <c r="K14" t="n">
-        <v>837</v>
+        <v>902</v>
       </c>
       <c r="L14" t="n">
-        <v>819.4</v>
+        <v>807.8</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>771</v>
+        <v>970</v>
       </c>
       <c r="C15" t="n">
-        <v>700</v>
+        <v>827</v>
       </c>
       <c r="D15" t="n">
-        <v>777</v>
+        <v>1000</v>
       </c>
       <c r="E15" t="n">
-        <v>878</v>
+        <v>934</v>
       </c>
       <c r="F15" t="n">
-        <v>1018</v>
+        <v>737</v>
       </c>
       <c r="G15" t="n">
-        <v>759</v>
+        <v>950</v>
       </c>
       <c r="H15" t="n">
-        <v>915</v>
+        <v>763</v>
       </c>
       <c r="I15" t="n">
+        <v>873</v>
+      </c>
+      <c r="J15" t="n">
+        <v>866</v>
+      </c>
+      <c r="K15" t="n">
         <v>896</v>
       </c>
-      <c r="J15" t="n">
-        <v>977</v>
-      </c>
-      <c r="K15" t="n">
-        <v>837</v>
-      </c>
       <c r="L15" t="n">
-        <v>852.8</v>
+        <v>881.6</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>865</v>
+        <v>884</v>
       </c>
       <c r="C16" t="n">
-        <v>905</v>
+        <v>881</v>
       </c>
       <c r="D16" t="n">
-        <v>939</v>
+        <v>1037</v>
       </c>
       <c r="E16" t="n">
-        <v>903</v>
+        <v>1004</v>
       </c>
       <c r="F16" t="n">
-        <v>1011</v>
+        <v>856</v>
       </c>
       <c r="G16" t="n">
-        <v>975</v>
+        <v>994</v>
       </c>
       <c r="H16" t="n">
-        <v>804</v>
+        <v>929</v>
       </c>
       <c r="I16" t="n">
-        <v>798</v>
+        <v>1024</v>
       </c>
       <c r="J16" t="n">
-        <v>827</v>
+        <v>931</v>
       </c>
       <c r="K16" t="n">
-        <v>866</v>
+        <v>879</v>
       </c>
       <c r="L16" t="n">
-        <v>889.3</v>
+        <v>941.9</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1066</v>
+        <v>768</v>
       </c>
       <c r="C17" t="n">
-        <v>816</v>
+        <v>837</v>
       </c>
       <c r="D17" t="n">
-        <v>833</v>
+        <v>851</v>
       </c>
       <c r="E17" t="n">
-        <v>796</v>
+        <v>701</v>
       </c>
       <c r="F17" t="n">
-        <v>830</v>
+        <v>862</v>
       </c>
       <c r="G17" t="n">
-        <v>1042</v>
+        <v>723</v>
       </c>
       <c r="H17" t="n">
-        <v>771</v>
+        <v>864</v>
       </c>
       <c r="I17" t="n">
-        <v>957</v>
+        <v>817</v>
       </c>
       <c r="J17" t="n">
-        <v>826</v>
+        <v>922</v>
       </c>
       <c r="K17" t="n">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="L17" t="n">
-        <v>871.5</v>
+        <v>812.6</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>896</v>
+        <v>842</v>
       </c>
       <c r="C18" t="n">
-        <v>811</v>
+        <v>793</v>
       </c>
       <c r="D18" t="n">
-        <v>928</v>
+        <v>887</v>
       </c>
       <c r="E18" t="n">
-        <v>1001</v>
+        <v>828</v>
       </c>
       <c r="F18" t="n">
-        <v>709</v>
+        <v>853</v>
       </c>
       <c r="G18" t="n">
-        <v>840</v>
+        <v>950</v>
       </c>
       <c r="H18" t="n">
-        <v>837</v>
+        <v>759</v>
       </c>
       <c r="I18" t="n">
-        <v>893</v>
+        <v>841</v>
       </c>
       <c r="J18" t="n">
-        <v>836</v>
+        <v>853</v>
       </c>
       <c r="K18" t="n">
-        <v>813</v>
+        <v>824</v>
       </c>
       <c r="L18" t="n">
-        <v>856.4</v>
+        <v>843</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>850</v>
+        <v>790</v>
       </c>
       <c r="C19" t="n">
-        <v>798</v>
+        <v>849</v>
       </c>
       <c r="D19" t="n">
-        <v>874</v>
+        <v>851</v>
       </c>
       <c r="E19" t="n">
-        <v>944</v>
+        <v>829</v>
       </c>
       <c r="F19" t="n">
-        <v>878</v>
+        <v>943</v>
       </c>
       <c r="G19" t="n">
-        <v>912</v>
+        <v>898</v>
       </c>
       <c r="H19" t="n">
-        <v>984</v>
+        <v>968</v>
       </c>
       <c r="I19" t="n">
-        <v>853</v>
+        <v>761</v>
       </c>
       <c r="J19" t="n">
-        <v>889</v>
+        <v>742</v>
       </c>
       <c r="K19" t="n">
-        <v>838</v>
+        <v>895</v>
       </c>
       <c r="L19" t="n">
-        <v>882</v>
+        <v>852.6</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1072</v>
+        <v>911</v>
       </c>
       <c r="C20" t="n">
-        <v>1032</v>
+        <v>944</v>
       </c>
       <c r="D20" t="n">
-        <v>980</v>
+        <v>952</v>
       </c>
       <c r="E20" t="n">
-        <v>868</v>
+        <v>955</v>
       </c>
       <c r="F20" t="n">
-        <v>1044</v>
+        <v>972</v>
       </c>
       <c r="G20" t="n">
-        <v>887</v>
+        <v>973</v>
       </c>
       <c r="H20" t="n">
-        <v>1038</v>
+        <v>853</v>
       </c>
       <c r="I20" t="n">
-        <v>978</v>
+        <v>1081</v>
       </c>
       <c r="J20" t="n">
-        <v>892</v>
+        <v>973</v>
       </c>
       <c r="K20" t="n">
-        <v>1033</v>
+        <v>801</v>
       </c>
       <c r="L20" t="n">
-        <v>982.4</v>
+        <v>941.5</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>802</v>
+        <v>922</v>
       </c>
       <c r="C21" t="n">
-        <v>921</v>
+        <v>866</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>868</v>
       </c>
       <c r="E21" t="n">
-        <v>822</v>
+        <v>860</v>
       </c>
       <c r="F21" t="n">
-        <v>806</v>
+        <v>845</v>
       </c>
       <c r="G21" t="n">
-        <v>824</v>
+        <v>835</v>
       </c>
       <c r="H21" t="n">
-        <v>769</v>
+        <v>847</v>
       </c>
       <c r="I21" t="n">
-        <v>800</v>
+        <v>826</v>
       </c>
       <c r="J21" t="n">
-        <v>811</v>
+        <v>876</v>
       </c>
       <c r="K21" t="n">
-        <v>967</v>
+        <v>882</v>
       </c>
       <c r="L21" t="n">
-        <v>831.4</v>
+        <v>862.7</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
+        <v>887</v>
+      </c>
+      <c r="C22" t="n">
+        <v>883</v>
+      </c>
+      <c r="D22" t="n">
+        <v>781</v>
+      </c>
+      <c r="E22" t="n">
         <v>792</v>
       </c>
-      <c r="C22" t="n">
-        <v>799</v>
-      </c>
-      <c r="D22" t="n">
-        <v>931</v>
-      </c>
-      <c r="E22" t="n">
-        <v>774</v>
-      </c>
       <c r="F22" t="n">
-        <v>771</v>
+        <v>815</v>
       </c>
       <c r="G22" t="n">
-        <v>987</v>
+        <v>785</v>
       </c>
       <c r="H22" t="n">
-        <v>876</v>
+        <v>745</v>
       </c>
       <c r="I22" t="n">
-        <v>810</v>
+        <v>911</v>
       </c>
       <c r="J22" t="n">
-        <v>745</v>
+        <v>837</v>
       </c>
       <c r="K22" t="n">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="L22" t="n">
-        <v>818.4</v>
+        <v>814.7</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1221</v>
+        <v>867</v>
       </c>
       <c r="C23" t="n">
-        <v>901</v>
+        <v>1065</v>
       </c>
       <c r="D23" t="n">
-        <v>847</v>
+        <v>1101</v>
       </c>
       <c r="E23" t="n">
-        <v>1066</v>
+        <v>940</v>
       </c>
       <c r="F23" t="n">
-        <v>991</v>
+        <v>1063</v>
       </c>
       <c r="G23" t="n">
-        <v>1162</v>
+        <v>1064</v>
       </c>
       <c r="H23" t="n">
-        <v>994</v>
+        <v>927</v>
       </c>
       <c r="I23" t="n">
-        <v>990</v>
+        <v>895</v>
       </c>
       <c r="J23" t="n">
-        <v>1120</v>
+        <v>1082</v>
       </c>
       <c r="K23" t="n">
-        <v>1098</v>
+        <v>1058</v>
       </c>
       <c r="L23" t="n">
-        <v>1039</v>
+        <v>1006.2</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>864</v>
+        <v>1062</v>
       </c>
       <c r="C24" t="n">
-        <v>812</v>
+        <v>1058</v>
       </c>
       <c r="D24" t="n">
-        <v>826</v>
+        <v>894</v>
       </c>
       <c r="E24" t="n">
-        <v>802</v>
+        <v>921</v>
       </c>
       <c r="F24" t="n">
-        <v>1034</v>
+        <v>951</v>
       </c>
       <c r="G24" t="n">
-        <v>999</v>
+        <v>837</v>
       </c>
       <c r="H24" t="n">
-        <v>905</v>
+        <v>924</v>
       </c>
       <c r="I24" t="n">
-        <v>976</v>
+        <v>810</v>
       </c>
       <c r="J24" t="n">
-        <v>899</v>
+        <v>995</v>
       </c>
       <c r="K24" t="n">
-        <v>827</v>
+        <v>927</v>
       </c>
       <c r="L24" t="n">
-        <v>894.4</v>
+        <v>937.9</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>877</v>
+        <v>930</v>
       </c>
       <c r="C25" t="n">
-        <v>796</v>
+        <v>876</v>
       </c>
       <c r="D25" t="n">
-        <v>1038</v>
+        <v>861</v>
       </c>
       <c r="E25" t="n">
-        <v>1075</v>
+        <v>911</v>
       </c>
       <c r="F25" t="n">
-        <v>830</v>
+        <v>895</v>
       </c>
       <c r="G25" t="n">
-        <v>811</v>
+        <v>836</v>
       </c>
       <c r="H25" t="n">
-        <v>881</v>
+        <v>824</v>
       </c>
       <c r="I25" t="n">
-        <v>882</v>
+        <v>905</v>
       </c>
       <c r="J25" t="n">
-        <v>879</v>
+        <v>1003</v>
       </c>
       <c r="K25" t="n">
-        <v>991</v>
+        <v>831</v>
       </c>
       <c r="L25" t="n">
-        <v>906</v>
+        <v>887.2</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>879</v>
+        <v>828</v>
       </c>
       <c r="C26" t="n">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D26" t="n">
-        <v>729</v>
+        <v>785</v>
       </c>
       <c r="E26" t="n">
-        <v>826</v>
+        <v>916</v>
       </c>
       <c r="F26" t="n">
-        <v>860</v>
+        <v>875</v>
       </c>
       <c r="G26" t="n">
-        <v>814</v>
+        <v>903</v>
       </c>
       <c r="H26" t="n">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="I26" t="n">
-        <v>877</v>
+        <v>761</v>
       </c>
       <c r="J26" t="n">
-        <v>892</v>
+        <v>759</v>
       </c>
       <c r="K26" t="n">
-        <v>892</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
-        <v>843.4</v>
+        <v>845.5</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1062</v>
+        <v>946</v>
       </c>
       <c r="C27" t="n">
-        <v>787</v>
+        <v>1081</v>
       </c>
       <c r="D27" t="n">
-        <v>987</v>
+        <v>951</v>
       </c>
       <c r="E27" t="n">
-        <v>916</v>
+        <v>937</v>
       </c>
       <c r="F27" t="n">
-        <v>920</v>
+        <v>866</v>
       </c>
       <c r="G27" t="n">
+        <v>917</v>
+      </c>
+      <c r="H27" t="n">
+        <v>873</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1142</v>
+      </c>
+      <c r="J27" t="n">
+        <v>782</v>
+      </c>
+      <c r="K27" t="n">
         <v>1010</v>
       </c>
-      <c r="H27" t="n">
-        <v>960</v>
-      </c>
-      <c r="I27" t="n">
-        <v>909</v>
-      </c>
-      <c r="J27" t="n">
-        <v>848</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1063</v>
-      </c>
       <c r="L27" t="n">
-        <v>946.2</v>
+        <v>950.5</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>913</v>
+        <v>805</v>
       </c>
       <c r="C28" t="n">
+        <v>887</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1013</v>
+      </c>
+      <c r="E28" t="n">
+        <v>933</v>
+      </c>
+      <c r="F28" t="n">
+        <v>933</v>
+      </c>
+      <c r="G28" t="n">
+        <v>829</v>
+      </c>
+      <c r="H28" t="n">
+        <v>977</v>
+      </c>
+      <c r="I28" t="n">
+        <v>912</v>
+      </c>
+      <c r="J28" t="n">
         <v>1027</v>
       </c>
-      <c r="D28" t="n">
-        <v>940</v>
-      </c>
-      <c r="E28" t="n">
-        <v>874</v>
-      </c>
-      <c r="F28" t="n">
-        <v>976</v>
-      </c>
-      <c r="G28" t="n">
-        <v>906</v>
-      </c>
-      <c r="H28" t="n">
-        <v>841</v>
-      </c>
-      <c r="I28" t="n">
-        <v>959</v>
-      </c>
-      <c r="J28" t="n">
-        <v>782</v>
-      </c>
       <c r="K28" t="n">
-        <v>921</v>
+        <v>878</v>
       </c>
       <c r="L28" t="n">
-        <v>913.9</v>
+        <v>919.4</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>763</v>
+        <v>772</v>
       </c>
       <c r="C29" t="n">
-        <v>890</v>
+        <v>837</v>
       </c>
       <c r="D29" t="n">
-        <v>839</v>
+        <v>804</v>
       </c>
       <c r="E29" t="n">
-        <v>886</v>
+        <v>910</v>
       </c>
       <c r="F29" t="n">
-        <v>745</v>
+        <v>837</v>
       </c>
       <c r="G29" t="n">
-        <v>832</v>
+        <v>979</v>
       </c>
       <c r="H29" t="n">
-        <v>973</v>
+        <v>835</v>
       </c>
       <c r="I29" t="n">
-        <v>810</v>
+        <v>862</v>
       </c>
       <c r="J29" t="n">
-        <v>781</v>
+        <v>912</v>
       </c>
       <c r="K29" t="n">
-        <v>801</v>
+        <v>933</v>
       </c>
       <c r="L29" t="n">
-        <v>832</v>
+        <v>868.1</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>839</v>
+        <v>800</v>
       </c>
       <c r="C30" t="n">
-        <v>815</v>
+        <v>914</v>
       </c>
       <c r="D30" t="n">
-        <v>784</v>
+        <v>915</v>
       </c>
       <c r="E30" t="n">
-        <v>767</v>
+        <v>936</v>
       </c>
       <c r="F30" t="n">
-        <v>802</v>
+        <v>889</v>
       </c>
       <c r="G30" t="n">
-        <v>984</v>
+        <v>955</v>
       </c>
       <c r="H30" t="n">
-        <v>862</v>
+        <v>772</v>
       </c>
       <c r="I30" t="n">
-        <v>795</v>
+        <v>881</v>
       </c>
       <c r="J30" t="n">
-        <v>800</v>
+        <v>846</v>
       </c>
       <c r="K30" t="n">
-        <v>757</v>
+        <v>832</v>
       </c>
       <c r="L30" t="n">
-        <v>820.5</v>
+        <v>874</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>754</v>
+        <v>832</v>
       </c>
       <c r="C31" t="n">
-        <v>804</v>
+        <v>909</v>
       </c>
       <c r="D31" t="n">
+        <v>795</v>
+      </c>
+      <c r="E31" t="n">
+        <v>967</v>
+      </c>
+      <c r="F31" t="n">
+        <v>919</v>
+      </c>
+      <c r="G31" t="n">
+        <v>867</v>
+      </c>
+      <c r="H31" t="n">
+        <v>954</v>
+      </c>
+      <c r="I31" t="n">
         <v>784</v>
       </c>
-      <c r="E31" t="n">
-        <v>864</v>
-      </c>
-      <c r="F31" t="n">
-        <v>775</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1033</v>
-      </c>
-      <c r="H31" t="n">
-        <v>939</v>
-      </c>
-      <c r="I31" t="n">
-        <v>884</v>
-      </c>
       <c r="J31" t="n">
-        <v>856</v>
+        <v>1014</v>
       </c>
       <c r="K31" t="n">
-        <v>848</v>
+        <v>945</v>
       </c>
       <c r="L31" t="n">
-        <v>854.1</v>
+        <v>898.6</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
+        <v>816</v>
+      </c>
+      <c r="C32" t="n">
+        <v>868</v>
+      </c>
+      <c r="D32" t="n">
+        <v>761</v>
+      </c>
+      <c r="E32" t="n">
+        <v>821</v>
+      </c>
+      <c r="F32" t="n">
+        <v>816</v>
+      </c>
+      <c r="G32" t="n">
         <v>854</v>
       </c>
-      <c r="C32" t="n">
-        <v>957</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1122</v>
-      </c>
-      <c r="E32" t="n">
-        <v>892</v>
-      </c>
-      <c r="F32" t="n">
-        <v>892</v>
-      </c>
-      <c r="G32" t="n">
-        <v>845</v>
-      </c>
       <c r="H32" t="n">
-        <v>925</v>
+        <v>956</v>
       </c>
       <c r="I32" t="n">
-        <v>788</v>
+        <v>762</v>
       </c>
       <c r="J32" t="n">
-        <v>871</v>
+        <v>859</v>
       </c>
       <c r="K32" t="n">
-        <v>820</v>
+        <v>932</v>
       </c>
       <c r="L32" t="n">
-        <v>896.6</v>
+        <v>844.5</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>824</v>
+        <v>892</v>
       </c>
       <c r="C33" t="n">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="D33" t="n">
-        <v>821</v>
+        <v>884</v>
       </c>
       <c r="E33" t="n">
-        <v>872</v>
+        <v>740</v>
       </c>
       <c r="F33" t="n">
-        <v>769</v>
+        <v>808</v>
       </c>
       <c r="G33" t="n">
-        <v>811</v>
+        <v>768</v>
       </c>
       <c r="H33" t="n">
-        <v>870</v>
+        <v>934</v>
       </c>
       <c r="I33" t="n">
-        <v>740</v>
+        <v>895</v>
       </c>
       <c r="J33" t="n">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="K33" t="n">
-        <v>855</v>
+        <v>820</v>
       </c>
       <c r="L33" t="n">
-        <v>817.5</v>
+        <v>834.8</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>863</v>
+        <v>707</v>
       </c>
       <c r="C34" t="n">
-        <v>820</v>
+        <v>781</v>
       </c>
       <c r="D34" t="n">
-        <v>877</v>
+        <v>764</v>
       </c>
       <c r="E34" t="n">
-        <v>749</v>
+        <v>816</v>
       </c>
       <c r="F34" t="n">
-        <v>789</v>
+        <v>726</v>
       </c>
       <c r="G34" t="n">
-        <v>673</v>
+        <v>702</v>
       </c>
       <c r="H34" t="n">
-        <v>903</v>
+        <v>862</v>
       </c>
       <c r="I34" t="n">
-        <v>739</v>
+        <v>837</v>
       </c>
       <c r="J34" t="n">
-        <v>780</v>
+        <v>856</v>
       </c>
       <c r="K34" t="n">
-        <v>866</v>
+        <v>838</v>
       </c>
       <c r="L34" t="n">
-        <v>805.9</v>
+        <v>788.9</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>915</v>
+        <v>948</v>
       </c>
       <c r="C35" t="n">
-        <v>752</v>
+        <v>861</v>
       </c>
       <c r="D35" t="n">
+        <v>873</v>
+      </c>
+      <c r="E35" t="n">
+        <v>845</v>
+      </c>
+      <c r="F35" t="n">
+        <v>923</v>
+      </c>
+      <c r="G35" t="n">
         <v>801</v>
       </c>
-      <c r="E35" t="n">
-        <v>703</v>
-      </c>
-      <c r="F35" t="n">
-        <v>719</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1016</v>
-      </c>
       <c r="H35" t="n">
-        <v>996</v>
+        <v>953</v>
       </c>
       <c r="I35" t="n">
-        <v>710</v>
+        <v>853</v>
       </c>
       <c r="J35" t="n">
-        <v>764</v>
+        <v>795</v>
       </c>
       <c r="K35" t="n">
-        <v>762</v>
+        <v>820</v>
       </c>
       <c r="L35" t="n">
-        <v>813.8</v>
+        <v>867.2</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>899</v>
+        <v>938</v>
       </c>
       <c r="C36" t="n">
-        <v>1155</v>
+        <v>848</v>
       </c>
       <c r="D36" t="n">
-        <v>906</v>
+        <v>940</v>
       </c>
       <c r="E36" t="n">
-        <v>807</v>
+        <v>1107</v>
       </c>
       <c r="F36" t="n">
-        <v>848</v>
+        <v>911</v>
       </c>
       <c r="G36" t="n">
-        <v>828</v>
+        <v>809</v>
       </c>
       <c r="H36" t="n">
-        <v>1049</v>
+        <v>867</v>
       </c>
       <c r="I36" t="n">
-        <v>835</v>
+        <v>1051</v>
       </c>
       <c r="J36" t="n">
-        <v>921</v>
+        <v>860</v>
       </c>
       <c r="K36" t="n">
-        <v>895</v>
+        <v>949</v>
       </c>
       <c r="L36" t="n">
-        <v>914.3</v>
+        <v>928</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>811</v>
+        <v>835</v>
       </c>
       <c r="C37" t="n">
-        <v>764</v>
+        <v>830</v>
       </c>
       <c r="D37" t="n">
-        <v>816</v>
+        <v>846</v>
       </c>
       <c r="E37" t="n">
-        <v>909</v>
+        <v>810</v>
       </c>
       <c r="F37" t="n">
-        <v>779</v>
+        <v>729</v>
       </c>
       <c r="G37" t="n">
-        <v>822</v>
+        <v>869</v>
       </c>
       <c r="H37" t="n">
-        <v>866</v>
+        <v>834</v>
       </c>
       <c r="I37" t="n">
-        <v>781</v>
+        <v>671</v>
       </c>
       <c r="J37" t="n">
-        <v>729</v>
+        <v>767</v>
       </c>
       <c r="K37" t="n">
-        <v>786</v>
+        <v>762</v>
       </c>
       <c r="L37" t="n">
-        <v>806.3</v>
+        <v>795.3</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>783</v>
+        <v>865</v>
       </c>
       <c r="C38" t="n">
-        <v>800</v>
+        <v>914</v>
       </c>
       <c r="D38" t="n">
-        <v>847</v>
+        <v>742</v>
       </c>
       <c r="E38" t="n">
-        <v>821</v>
+        <v>884</v>
       </c>
       <c r="F38" t="n">
-        <v>743</v>
+        <v>778</v>
       </c>
       <c r="G38" t="n">
-        <v>852</v>
+        <v>916</v>
       </c>
       <c r="H38" t="n">
-        <v>772</v>
+        <v>833</v>
       </c>
       <c r="I38" t="n">
-        <v>814</v>
+        <v>908</v>
       </c>
       <c r="J38" t="n">
-        <v>975</v>
+        <v>909</v>
       </c>
       <c r="K38" t="n">
-        <v>760</v>
+        <v>834</v>
       </c>
       <c r="L38" t="n">
-        <v>816.7</v>
+        <v>858.3</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>766</v>
+        <v>815</v>
       </c>
       <c r="C39" t="n">
-        <v>884</v>
+        <v>824</v>
       </c>
       <c r="D39" t="n">
-        <v>961</v>
+        <v>777</v>
       </c>
       <c r="E39" t="n">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F39" t="n">
-        <v>925</v>
+        <v>737</v>
       </c>
       <c r="G39" t="n">
-        <v>687</v>
+        <v>775</v>
       </c>
       <c r="H39" t="n">
-        <v>794</v>
+        <v>1014</v>
       </c>
       <c r="I39" t="n">
-        <v>782</v>
+        <v>861</v>
       </c>
       <c r="J39" t="n">
-        <v>774</v>
+        <v>954</v>
       </c>
       <c r="K39" t="n">
-        <v>917</v>
+        <v>771</v>
       </c>
       <c r="L39" t="n">
-        <v>826.3</v>
+        <v>829.8</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>828</v>
+        <v>881</v>
       </c>
       <c r="C40" t="n">
-        <v>791</v>
+        <v>888</v>
       </c>
       <c r="D40" t="n">
-        <v>910</v>
+        <v>831</v>
       </c>
       <c r="E40" t="n">
-        <v>780</v>
+        <v>812</v>
       </c>
       <c r="F40" t="n">
-        <v>829</v>
+        <v>928</v>
       </c>
       <c r="G40" t="n">
-        <v>801</v>
+        <v>824</v>
       </c>
       <c r="H40" t="n">
-        <v>807</v>
+        <v>1189</v>
       </c>
       <c r="I40" t="n">
-        <v>930</v>
+        <v>988</v>
       </c>
       <c r="J40" t="n">
-        <v>842</v>
+        <v>851</v>
       </c>
       <c r="K40" t="n">
-        <v>893</v>
+        <v>817</v>
       </c>
       <c r="L40" t="n">
-        <v>841.1</v>
+        <v>900.9</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>955</v>
+        <v>1025</v>
       </c>
       <c r="C41" t="n">
-        <v>796</v>
+        <v>742</v>
       </c>
       <c r="D41" t="n">
-        <v>883</v>
+        <v>804</v>
       </c>
       <c r="E41" t="n">
-        <v>804</v>
+        <v>888</v>
       </c>
       <c r="F41" t="n">
-        <v>946</v>
+        <v>829</v>
       </c>
       <c r="G41" t="n">
-        <v>765</v>
+        <v>952</v>
       </c>
       <c r="H41" t="n">
-        <v>894</v>
+        <v>919</v>
       </c>
       <c r="I41" t="n">
-        <v>842</v>
+        <v>865</v>
       </c>
       <c r="J41" t="n">
-        <v>827</v>
+        <v>816</v>
       </c>
       <c r="K41" t="n">
-        <v>759</v>
+        <v>924</v>
       </c>
       <c r="L41" t="n">
-        <v>847.1</v>
+        <v>876.4</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>714</v>
+        <v>834</v>
       </c>
       <c r="C42" t="n">
-        <v>684</v>
+        <v>744</v>
       </c>
       <c r="D42" t="n">
-        <v>738</v>
+        <v>724</v>
       </c>
       <c r="E42" t="n">
-        <v>871</v>
+        <v>705</v>
       </c>
       <c r="F42" t="n">
-        <v>742</v>
+        <v>826</v>
       </c>
       <c r="G42" t="n">
-        <v>757</v>
+        <v>1018</v>
       </c>
       <c r="H42" t="n">
-        <v>712</v>
+        <v>761</v>
       </c>
       <c r="I42" t="n">
-        <v>720</v>
+        <v>737</v>
       </c>
       <c r="J42" t="n">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="K42" t="n">
-        <v>669</v>
+        <v>732</v>
       </c>
       <c r="L42" t="n">
-        <v>726.1</v>
+        <v>774.3</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>860</v>
+        <v>754</v>
       </c>
       <c r="C43" t="n">
-        <v>825</v>
+        <v>895</v>
       </c>
       <c r="D43" t="n">
-        <v>907</v>
+        <v>889</v>
       </c>
       <c r="E43" t="n">
-        <v>870</v>
+        <v>933</v>
       </c>
       <c r="F43" t="n">
-        <v>786</v>
+        <v>886</v>
       </c>
       <c r="G43" t="n">
-        <v>794</v>
+        <v>873</v>
       </c>
       <c r="H43" t="n">
-        <v>884</v>
+        <v>715</v>
       </c>
       <c r="I43" t="n">
-        <v>831</v>
+        <v>908</v>
       </c>
       <c r="J43" t="n">
-        <v>878</v>
+        <v>781</v>
       </c>
       <c r="K43" t="n">
-        <v>733</v>
+        <v>781</v>
       </c>
       <c r="L43" t="n">
-        <v>836.8</v>
+        <v>841.5</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>844</v>
+        <v>965</v>
       </c>
       <c r="C44" t="n">
-        <v>774</v>
+        <v>867</v>
       </c>
       <c r="D44" t="n">
-        <v>792</v>
+        <v>810</v>
       </c>
       <c r="E44" t="n">
-        <v>819</v>
+        <v>889</v>
       </c>
       <c r="F44" t="n">
+        <v>867</v>
+      </c>
+      <c r="G44" t="n">
+        <v>876</v>
+      </c>
+      <c r="H44" t="n">
         <v>805</v>
       </c>
-      <c r="G44" t="n">
-        <v>1038</v>
-      </c>
-      <c r="H44" t="n">
-        <v>951</v>
-      </c>
       <c r="I44" t="n">
-        <v>888</v>
+        <v>867</v>
       </c>
       <c r="J44" t="n">
-        <v>921</v>
+        <v>794</v>
       </c>
       <c r="K44" t="n">
-        <v>901</v>
+        <v>773</v>
       </c>
       <c r="L44" t="n">
-        <v>873.3</v>
+        <v>851.3</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1036</v>
+        <v>832</v>
       </c>
       <c r="C45" t="n">
-        <v>840</v>
+        <v>1048</v>
       </c>
       <c r="D45" t="n">
-        <v>901</v>
+        <v>981</v>
       </c>
       <c r="E45" t="n">
-        <v>994</v>
+        <v>892</v>
       </c>
       <c r="F45" t="n">
-        <v>835</v>
+        <v>858</v>
       </c>
       <c r="G45" t="n">
-        <v>791</v>
+        <v>941</v>
       </c>
       <c r="H45" t="n">
-        <v>942</v>
+        <v>865</v>
       </c>
       <c r="I45" t="n">
-        <v>897</v>
+        <v>985</v>
       </c>
       <c r="J45" t="n">
-        <v>957</v>
+        <v>889</v>
       </c>
       <c r="K45" t="n">
-        <v>910</v>
+        <v>1000</v>
       </c>
       <c r="L45" t="n">
-        <v>910.3</v>
+        <v>929.1</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>792</v>
+        <v>900</v>
       </c>
       <c r="C46" t="n">
-        <v>901</v>
+        <v>823</v>
       </c>
       <c r="D46" t="n">
-        <v>799</v>
+        <v>929</v>
       </c>
       <c r="E46" t="n">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="F46" t="n">
-        <v>985</v>
+        <v>1014</v>
       </c>
       <c r="G46" t="n">
-        <v>952</v>
+        <v>1008</v>
       </c>
       <c r="H46" t="n">
-        <v>765</v>
+        <v>978</v>
       </c>
       <c r="I46" t="n">
-        <v>861</v>
+        <v>927</v>
       </c>
       <c r="J46" t="n">
-        <v>1001</v>
+        <v>841</v>
       </c>
       <c r="K46" t="n">
-        <v>896</v>
+        <v>915</v>
       </c>
       <c r="L46" t="n">
-        <v>888.1</v>
+        <v>925.6</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>819</v>
+        <v>873</v>
       </c>
       <c r="C47" t="n">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="D47" t="n">
-        <v>828</v>
+        <v>967</v>
       </c>
       <c r="E47" t="n">
-        <v>825</v>
+        <v>1039</v>
       </c>
       <c r="F47" t="n">
-        <v>849</v>
+        <v>968</v>
       </c>
       <c r="G47" t="n">
-        <v>914</v>
+        <v>902</v>
       </c>
       <c r="H47" t="n">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="I47" t="n">
-        <v>915</v>
+        <v>941</v>
       </c>
       <c r="J47" t="n">
-        <v>969</v>
+        <v>951</v>
       </c>
       <c r="K47" t="n">
-        <v>952</v>
+        <v>933</v>
       </c>
       <c r="L47" t="n">
-        <v>904.3</v>
+        <v>954.8</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>883</v>
+        <v>759</v>
       </c>
       <c r="C48" t="n">
-        <v>941</v>
+        <v>816</v>
       </c>
       <c r="D48" t="n">
-        <v>795</v>
+        <v>908</v>
       </c>
       <c r="E48" t="n">
-        <v>884</v>
+        <v>844</v>
       </c>
       <c r="F48" t="n">
-        <v>797</v>
+        <v>956</v>
       </c>
       <c r="G48" t="n">
-        <v>868</v>
+        <v>682</v>
       </c>
       <c r="H48" t="n">
-        <v>910</v>
+        <v>818</v>
       </c>
       <c r="I48" t="n">
-        <v>855</v>
+        <v>743</v>
       </c>
       <c r="J48" t="n">
-        <v>723</v>
+        <v>890</v>
       </c>
       <c r="K48" t="n">
-        <v>917</v>
+        <v>789</v>
       </c>
       <c r="L48" t="n">
-        <v>857.3</v>
+        <v>820.5</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>959</v>
+        <v>879</v>
       </c>
       <c r="C49" t="n">
-        <v>855</v>
+        <v>903</v>
       </c>
       <c r="D49" t="n">
-        <v>875</v>
+        <v>773</v>
       </c>
       <c r="E49" t="n">
-        <v>919</v>
+        <v>964</v>
       </c>
       <c r="F49" t="n">
-        <v>1127</v>
+        <v>960</v>
       </c>
       <c r="G49" t="n">
-        <v>840</v>
+        <v>797</v>
       </c>
       <c r="H49" t="n">
-        <v>806</v>
+        <v>942</v>
       </c>
       <c r="I49" t="n">
-        <v>939</v>
+        <v>880</v>
       </c>
       <c r="J49" t="n">
-        <v>835</v>
+        <v>892</v>
       </c>
       <c r="K49" t="n">
-        <v>844</v>
+        <v>892</v>
       </c>
       <c r="L49" t="n">
-        <v>899.9</v>
+        <v>888.2</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>866</v>
+        <v>909</v>
       </c>
       <c r="C50" t="n">
-        <v>986</v>
+        <v>900</v>
       </c>
       <c r="D50" t="n">
-        <v>869</v>
+        <v>960</v>
       </c>
       <c r="E50" t="n">
-        <v>1015</v>
+        <v>848</v>
       </c>
       <c r="F50" t="n">
-        <v>961</v>
+        <v>848</v>
       </c>
       <c r="G50" t="n">
-        <v>898</v>
+        <v>886</v>
       </c>
       <c r="H50" t="n">
-        <v>997</v>
+        <v>903</v>
       </c>
       <c r="I50" t="n">
-        <v>868</v>
+        <v>849</v>
       </c>
       <c r="J50" t="n">
-        <v>870</v>
+        <v>825</v>
       </c>
       <c r="K50" t="n">
-        <v>772</v>
+        <v>985</v>
       </c>
       <c r="L50" t="n">
-        <v>910.2</v>
+        <v>891.3</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>892</v>
+        <v>862</v>
       </c>
       <c r="C51" t="n">
         <v>850</v>
       </c>
       <c r="D51" t="n">
-        <v>803</v>
+        <v>1003</v>
       </c>
       <c r="E51" t="n">
-        <v>791</v>
+        <v>777</v>
       </c>
       <c r="F51" t="n">
-        <v>903</v>
+        <v>801</v>
       </c>
       <c r="G51" t="n">
-        <v>888</v>
+        <v>956</v>
       </c>
       <c r="H51" t="n">
-        <v>905</v>
+        <v>852</v>
       </c>
       <c r="I51" t="n">
-        <v>1037</v>
+        <v>823</v>
       </c>
       <c r="J51" t="n">
-        <v>821</v>
+        <v>940</v>
       </c>
       <c r="K51" t="n">
-        <v>810</v>
+        <v>892</v>
       </c>
       <c r="L51" t="n">
-        <v>870</v>
+        <v>875.6</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>869.26</v>
+        <v>859.14</v>
       </c>
       <c r="C52" t="n">
-        <v>845.16</v>
+        <v>871.98</v>
       </c>
       <c r="D52" t="n">
-        <v>859.84</v>
+        <v>861.88</v>
       </c>
       <c r="E52" t="n">
-        <v>850.26</v>
+        <v>868.1</v>
       </c>
       <c r="F52" t="n">
-        <v>859.52</v>
+        <v>856.46</v>
       </c>
       <c r="G52" t="n">
-        <v>857.54</v>
+        <v>883.14</v>
       </c>
       <c r="H52" t="n">
-        <v>879.1</v>
+        <v>866.52</v>
       </c>
       <c r="I52" t="n">
-        <v>855.4400000000001</v>
+        <v>867.9</v>
       </c>
       <c r="J52" t="n">
-        <v>854.04</v>
+        <v>861.2</v>
       </c>
       <c r="K52" t="n">
-        <v>857.36</v>
+        <v>870.5599999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>858.752</v>
+        <v>866.688</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>6.580253601074219</v>
+        <v>7.040679693222046</v>
       </c>
       <c r="C2" t="n">
-        <v>7.217751502990723</v>
+        <v>7.131952047348022</v>
       </c>
       <c r="D2" t="n">
-        <v>6.350331544876099</v>
+        <v>7.966262102127075</v>
       </c>
       <c r="E2" t="n">
-        <v>6.913912534713745</v>
+        <v>8.886884927749634</v>
       </c>
       <c r="F2" t="n">
-        <v>6.294478416442871</v>
+        <v>6.861640214920044</v>
       </c>
       <c r="G2" t="n">
-        <v>6.362314462661743</v>
+        <v>8.583644866943359</v>
       </c>
       <c r="H2" t="n">
-        <v>7.978684425354004</v>
+        <v>8.861911058425903</v>
       </c>
       <c r="I2" t="n">
-        <v>6.818656444549561</v>
+        <v>8.747709274291992</v>
       </c>
       <c r="J2" t="n">
-        <v>8.417645454406738</v>
+        <v>7.969234704971313</v>
       </c>
       <c r="K2" t="n">
-        <v>6.123876571655273</v>
+        <v>8.896792888641357</v>
       </c>
       <c r="L2" t="n">
-        <v>6.905790495872497</v>
+        <v>8.094671177864075</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>6.913915634155273</v>
+        <v>7.178195953369141</v>
       </c>
       <c r="C3" t="n">
-        <v>6.316415309906006</v>
+        <v>7.339316129684448</v>
       </c>
       <c r="D3" t="n">
-        <v>6.551443576812744</v>
+        <v>9.585037231445312</v>
       </c>
       <c r="E3" t="n">
-        <v>8.265239000320435</v>
+        <v>7.448526620864868</v>
       </c>
       <c r="F3" t="n">
-        <v>8.383660554885864</v>
+        <v>7.354790687561035</v>
       </c>
       <c r="G3" t="n">
-        <v>7.106925964355469</v>
+        <v>7.016111373901367</v>
       </c>
       <c r="H3" t="n">
-        <v>8.79957914352417</v>
+        <v>7.560218811035156</v>
       </c>
       <c r="I3" t="n">
-        <v>6.521918296813965</v>
+        <v>8.298330068588257</v>
       </c>
       <c r="J3" t="n">
-        <v>6.614174604415894</v>
+        <v>7.648132085800171</v>
       </c>
       <c r="K3" t="n">
-        <v>9.091328620910645</v>
+        <v>9.420459270477295</v>
       </c>
       <c r="L3" t="n">
-        <v>7.456460070610047</v>
+        <v>7.884911823272705</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>6.276501655578613</v>
+        <v>9.365102767944336</v>
       </c>
       <c r="C4" t="n">
-        <v>6.971259117126465</v>
+        <v>7.869353294372559</v>
       </c>
       <c r="D4" t="n">
-        <v>9.031988382339478</v>
+        <v>8.505859851837158</v>
       </c>
       <c r="E4" t="n">
-        <v>6.61714243888855</v>
+        <v>7.179322957992554</v>
       </c>
       <c r="F4" t="n">
-        <v>9.447175979614258</v>
+        <v>6.679107666015625</v>
       </c>
       <c r="G4" t="n">
-        <v>6.230135440826416</v>
+        <v>6.713027238845825</v>
       </c>
       <c r="H4" t="n">
-        <v>6.697443723678589</v>
+        <v>7.135923624038696</v>
       </c>
       <c r="I4" t="n">
-        <v>6.281553268432617</v>
+        <v>8.500375986099243</v>
       </c>
       <c r="J4" t="n">
-        <v>7.471963405609131</v>
+        <v>6.577390909194946</v>
       </c>
       <c r="K4" t="n">
-        <v>6.078026056289673</v>
+        <v>7.906943082809448</v>
       </c>
       <c r="L4" t="n">
-        <v>7.110318946838379</v>
+        <v>7.643240737915039</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>5.623685598373413</v>
+        <v>6.819254159927368</v>
       </c>
       <c r="C5" t="n">
-        <v>5.582783460617065</v>
+        <v>7.774260520935059</v>
       </c>
       <c r="D5" t="n">
-        <v>6.071533203125</v>
+        <v>6.154979944229126</v>
       </c>
       <c r="E5" t="n">
-        <v>5.789275407791138</v>
+        <v>6.375913381576538</v>
       </c>
       <c r="F5" t="n">
-        <v>6.16534423828125</v>
+        <v>6.697073936462402</v>
       </c>
       <c r="G5" t="n">
-        <v>5.920425653457642</v>
+        <v>8.925309658050537</v>
       </c>
       <c r="H5" t="n">
-        <v>6.492000579833984</v>
+        <v>6.801407814025879</v>
       </c>
       <c r="I5" t="n">
-        <v>8.105334758758545</v>
+        <v>6.451219081878662</v>
       </c>
       <c r="J5" t="n">
-        <v>6.193245887756348</v>
+        <v>6.146031618118286</v>
       </c>
       <c r="K5" t="n">
-        <v>5.726901054382324</v>
+        <v>6.572376489639282</v>
       </c>
       <c r="L5" t="n">
-        <v>6.167052984237671</v>
+        <v>6.871782660484314</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>5.769789934158325</v>
+        <v>6.334529638290405</v>
       </c>
       <c r="C6" t="n">
-        <v>5.717972755432129</v>
+        <v>6.734968900680542</v>
       </c>
       <c r="D6" t="n">
-        <v>5.632663488388062</v>
+        <v>5.680203676223755</v>
       </c>
       <c r="E6" t="n">
-        <v>6.249653339385986</v>
+        <v>5.667770385742188</v>
       </c>
       <c r="F6" t="n">
-        <v>5.575279712677002</v>
+        <v>8.519351005554199</v>
       </c>
       <c r="G6" t="n">
-        <v>5.401258230209351</v>
+        <v>6.993794441223145</v>
       </c>
       <c r="H6" t="n">
-        <v>7.215625524520874</v>
+        <v>5.613417387008667</v>
       </c>
       <c r="I6" t="n">
-        <v>6.799700260162354</v>
+        <v>6.121606826782227</v>
       </c>
       <c r="J6" t="n">
-        <v>5.812180757522583</v>
+        <v>5.932067394256592</v>
       </c>
       <c r="K6" t="n">
-        <v>5.435180425643921</v>
+        <v>7.584245681762695</v>
       </c>
       <c r="L6" t="n">
-        <v>5.960930442810058</v>
+        <v>6.518195533752442</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>7.200678586959839</v>
+        <v>7.885951280593872</v>
       </c>
       <c r="C7" t="n">
-        <v>8.886859893798828</v>
+        <v>8.934266805648804</v>
       </c>
       <c r="D7" t="n">
-        <v>8.869458198547363</v>
+        <v>7.54685115814209</v>
       </c>
       <c r="E7" t="n">
-        <v>6.93734884262085</v>
+        <v>7.855567932128906</v>
       </c>
       <c r="F7" t="n">
-        <v>6.907397031784058</v>
+        <v>7.496972799301147</v>
       </c>
       <c r="G7" t="n">
-        <v>6.723881721496582</v>
+        <v>10.12813496589661</v>
       </c>
       <c r="H7" t="n">
-        <v>7.420130968093872</v>
+        <v>7.232190608978271</v>
       </c>
       <c r="I7" t="n">
-        <v>7.203210115432739</v>
+        <v>8.484914302825928</v>
       </c>
       <c r="J7" t="n">
-        <v>8.520873308181763</v>
+        <v>7.874984264373779</v>
       </c>
       <c r="K7" t="n">
-        <v>7.979660272598267</v>
+        <v>7.26408314704895</v>
       </c>
       <c r="L7" t="n">
-        <v>7.664949893951416</v>
+        <v>8.070391726493835</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>6.957314252853394</v>
+        <v>7.247080564498901</v>
       </c>
       <c r="C8" t="n">
-        <v>8.160703420639038</v>
+        <v>8.060436010360718</v>
       </c>
       <c r="D8" t="n">
-        <v>8.049516916275024</v>
+        <v>6.83757472038269</v>
       </c>
       <c r="E8" t="n">
-        <v>6.311434268951416</v>
+        <v>6.864020824432373</v>
       </c>
       <c r="F8" t="n">
-        <v>6.97224497795105</v>
+        <v>7.414551496505737</v>
       </c>
       <c r="G8" t="n">
-        <v>6.642075061798096</v>
+        <v>7.624605417251587</v>
       </c>
       <c r="H8" t="n">
-        <v>6.556806802749634</v>
+        <v>7.427057027816772</v>
       </c>
       <c r="I8" t="n">
-        <v>6.849075317382812</v>
+        <v>7.526335954666138</v>
       </c>
       <c r="J8" t="n">
-        <v>7.03510570526123</v>
+        <v>8.206106901168823</v>
       </c>
       <c r="K8" t="n">
-        <v>8.782869100570679</v>
+        <v>9.077347755432129</v>
       </c>
       <c r="L8" t="n">
-        <v>7.231714582443237</v>
+        <v>7.628511667251587</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>8.589169502258301</v>
+        <v>8.626020431518555</v>
       </c>
       <c r="C9" t="n">
-        <v>6.460694074630737</v>
+        <v>8.101872682571411</v>
       </c>
       <c r="D9" t="n">
-        <v>6.561418533325195</v>
+        <v>7.290384769439697</v>
       </c>
       <c r="E9" t="n">
-        <v>7.330438613891602</v>
+        <v>7.742277383804321</v>
       </c>
       <c r="F9" t="n">
-        <v>6.733515501022339</v>
+        <v>7.663494825363159</v>
       </c>
       <c r="G9" t="n">
-        <v>6.595346212387085</v>
+        <v>9.6678626537323</v>
       </c>
       <c r="H9" t="n">
-        <v>6.938015222549438</v>
+        <v>7.232550144195557</v>
       </c>
       <c r="I9" t="n">
-        <v>7.166151285171509</v>
+        <v>6.959771394729614</v>
       </c>
       <c r="J9" t="n">
-        <v>8.902835607528687</v>
+        <v>7.523336410522461</v>
       </c>
       <c r="K9" t="n">
-        <v>8.099886178970337</v>
+        <v>7.666987180709839</v>
       </c>
       <c r="L9" t="n">
-        <v>7.337747073173523</v>
+        <v>7.847455787658691</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>8.149243116378784</v>
+        <v>8.80253005027771</v>
       </c>
       <c r="C10" t="n">
-        <v>6.478492021560669</v>
+        <v>8.315288782119751</v>
       </c>
       <c r="D10" t="n">
-        <v>6.151344537734985</v>
+        <v>6.965741395950317</v>
       </c>
       <c r="E10" t="n">
-        <v>5.894987821578979</v>
+        <v>9.477322101593018</v>
       </c>
       <c r="F10" t="n">
-        <v>8.041034460067749</v>
+        <v>6.99665641784668</v>
       </c>
       <c r="G10" t="n">
-        <v>6.885487794876099</v>
+        <v>9.314752340316772</v>
       </c>
       <c r="H10" t="n">
-        <v>6.035165786743164</v>
+        <v>8.072926044464111</v>
       </c>
       <c r="I10" t="n">
-        <v>7.582188129425049</v>
+        <v>6.631097078323364</v>
       </c>
       <c r="J10" t="n">
-        <v>6.313445568084717</v>
+        <v>6.805634498596191</v>
       </c>
       <c r="K10" t="n">
-        <v>8.178199529647827</v>
+        <v>8.630003213882446</v>
       </c>
       <c r="L10" t="n">
-        <v>6.970958876609802</v>
+        <v>8.001195192337036</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>8.491447448730469</v>
+        <v>7.284921884536743</v>
       </c>
       <c r="C11" t="n">
-        <v>6.383433103561401</v>
+        <v>6.937808990478516</v>
       </c>
       <c r="D11" t="n">
-        <v>6.432272434234619</v>
+        <v>6.87406587600708</v>
       </c>
       <c r="E11" t="n">
-        <v>6.59235954284668</v>
+        <v>7.586203336715698</v>
       </c>
       <c r="F11" t="n">
-        <v>6.411333322525024</v>
+        <v>6.844094514846802</v>
       </c>
       <c r="G11" t="n">
-        <v>6.359472513198853</v>
+        <v>7.983133792877197</v>
       </c>
       <c r="H11" t="n">
-        <v>6.131540060043335</v>
+        <v>6.834105730056763</v>
       </c>
       <c r="I11" t="n">
-        <v>6.25313663482666</v>
+        <v>7.703355312347412</v>
       </c>
       <c r="J11" t="n">
-        <v>6.256585121154785</v>
+        <v>7.273961067199707</v>
       </c>
       <c r="K11" t="n">
-        <v>6.086024284362793</v>
+        <v>7.598503351211548</v>
       </c>
       <c r="L11" t="n">
-        <v>6.539760446548462</v>
+        <v>7.292015385627747</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>6.785224676132202</v>
+        <v>10.9764301776886</v>
       </c>
       <c r="C12" t="n">
-        <v>6.801684617996216</v>
+        <v>9.02553653717041</v>
       </c>
       <c r="D12" t="n">
-        <v>6.665552616119385</v>
+        <v>6.856136083602905</v>
       </c>
       <c r="E12" t="n">
-        <v>6.820669889450073</v>
+        <v>7.300525426864624</v>
       </c>
       <c r="F12" t="n">
-        <v>9.615541219711304</v>
+        <v>6.890547513961792</v>
       </c>
       <c r="G12" t="n">
-        <v>9.992045879364014</v>
+        <v>9.342180967330933</v>
       </c>
       <c r="H12" t="n">
-        <v>7.182716131210327</v>
+        <v>7.795755624771118</v>
       </c>
       <c r="I12" t="n">
-        <v>6.783774852752686</v>
+        <v>7.28302001953125</v>
       </c>
       <c r="J12" t="n">
-        <v>7.283468246459961</v>
+        <v>9.552142858505249</v>
       </c>
       <c r="K12" t="n">
-        <v>9.45343542098999</v>
+        <v>7.688982963562012</v>
       </c>
       <c r="L12" t="n">
-        <v>7.738411355018616</v>
+        <v>8.27112581729889</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>5.815175294876099</v>
+        <v>6.431249141693115</v>
       </c>
       <c r="C13" t="n">
-        <v>6.272577047348022</v>
+        <v>8.242571115493774</v>
       </c>
       <c r="D13" t="n">
-        <v>6.308936357498169</v>
+        <v>6.516058206558228</v>
       </c>
       <c r="E13" t="n">
-        <v>6.138370990753174</v>
+        <v>7.955240488052368</v>
       </c>
       <c r="F13" t="n">
-        <v>5.786751270294189</v>
+        <v>6.307417631149292</v>
       </c>
       <c r="G13" t="n">
-        <v>5.918432712554932</v>
+        <v>6.487004995346069</v>
       </c>
       <c r="H13" t="n">
-        <v>5.982792139053345</v>
+        <v>6.2241530418396</v>
       </c>
       <c r="I13" t="n">
-        <v>5.626670837402344</v>
+        <v>6.827602624893188</v>
       </c>
       <c r="J13" t="n">
-        <v>7.852508068084717</v>
+        <v>6.569291830062866</v>
       </c>
       <c r="K13" t="n">
-        <v>6.236105442047119</v>
+        <v>6.43459415435791</v>
       </c>
       <c r="L13" t="n">
-        <v>6.193832015991211</v>
+        <v>6.799518322944641</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>9.890315532684326</v>
+        <v>8.175181865692139</v>
       </c>
       <c r="C14" t="n">
-        <v>7.007683992385864</v>
+        <v>7.673435688018799</v>
       </c>
       <c r="D14" t="n">
-        <v>7.37922739982605</v>
+        <v>7.491396427154541</v>
       </c>
       <c r="E14" t="n">
-        <v>6.682515382766724</v>
+        <v>7.451004266738892</v>
       </c>
       <c r="F14" t="n">
-        <v>7.416121959686279</v>
+        <v>7.387164831161499</v>
       </c>
       <c r="G14" t="n">
-        <v>6.649072408676147</v>
+        <v>7.071486473083496</v>
       </c>
       <c r="H14" t="n">
-        <v>7.131885766983032</v>
+        <v>7.673470497131348</v>
       </c>
       <c r="I14" t="n">
-        <v>7.191871643066406</v>
+        <v>8.892824172973633</v>
       </c>
       <c r="J14" t="n">
-        <v>7.301911592483521</v>
+        <v>7.418108463287354</v>
       </c>
       <c r="K14" t="n">
-        <v>7.105428695678711</v>
+        <v>8.06345796585083</v>
       </c>
       <c r="L14" t="n">
-        <v>7.375603437423706</v>
+        <v>7.729753065109253</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>7.569222211837769</v>
+        <v>8.416066884994507</v>
       </c>
       <c r="C15" t="n">
-        <v>5.836167812347412</v>
+        <v>8.027035236358643</v>
       </c>
       <c r="D15" t="n">
-        <v>6.422181129455566</v>
+        <v>9.199014663696289</v>
       </c>
       <c r="E15" t="n">
-        <v>6.993699073791504</v>
+        <v>8.85694432258606</v>
       </c>
       <c r="F15" t="n">
-        <v>7.566727161407471</v>
+        <v>6.885484457015991</v>
       </c>
       <c r="G15" t="n">
-        <v>6.920879602432251</v>
+        <v>7.71212363243103</v>
       </c>
       <c r="H15" t="n">
-        <v>8.490899801254272</v>
+        <v>6.960292816162109</v>
       </c>
       <c r="I15" t="n">
-        <v>8.485402584075928</v>
+        <v>7.256536245346069</v>
       </c>
       <c r="J15" t="n">
-        <v>7.726854085922241</v>
+        <v>7.451522827148438</v>
       </c>
       <c r="K15" t="n">
-        <v>7.163168907165527</v>
+        <v>6.918876886367798</v>
       </c>
       <c r="L15" t="n">
-        <v>7.317520236968994</v>
+        <v>7.768389797210693</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>7.94283390045166</v>
+        <v>6.990686416625977</v>
       </c>
       <c r="C16" t="n">
-        <v>7.39181661605835</v>
+        <v>7.051135063171387</v>
       </c>
       <c r="D16" t="n">
-        <v>6.77087140083313</v>
+        <v>10.43824625015259</v>
       </c>
       <c r="E16" t="n">
-        <v>6.972879648208618</v>
+        <v>9.051916599273682</v>
       </c>
       <c r="F16" t="n">
-        <v>7.509958267211914</v>
+        <v>6.714389562606812</v>
       </c>
       <c r="G16" t="n">
-        <v>8.18971061706543</v>
+        <v>8.434553146362305</v>
       </c>
       <c r="H16" t="n">
-        <v>6.314096689224243</v>
+        <v>7.277933120727539</v>
       </c>
       <c r="I16" t="n">
-        <v>6.662948608398438</v>
+        <v>7.588250398635864</v>
       </c>
       <c r="J16" t="n">
-        <v>6.556793928146362</v>
+        <v>7.093539714813232</v>
       </c>
       <c r="K16" t="n">
-        <v>7.229098796844482</v>
+        <v>7.719437122344971</v>
       </c>
       <c r="L16" t="n">
-        <v>7.154100847244263</v>
+        <v>7.836008739471436</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>7.88292384147644</v>
+        <v>7.261116027832031</v>
       </c>
       <c r="C17" t="n">
-        <v>6.655543804168701</v>
+        <v>7.253116607666016</v>
       </c>
       <c r="D17" t="n">
-        <v>7.077997922897339</v>
+        <v>7.666539192199707</v>
       </c>
       <c r="E17" t="n">
-        <v>6.956324338912964</v>
+        <v>7.525449991226196</v>
       </c>
       <c r="F17" t="n">
-        <v>7.132280826568604</v>
+        <v>7.761305093765259</v>
       </c>
       <c r="G17" t="n">
-        <v>9.403537750244141</v>
+        <v>7.053138494491577</v>
       </c>
       <c r="H17" t="n">
-        <v>6.544463157653809</v>
+        <v>7.822647094726562</v>
       </c>
       <c r="I17" t="n">
-        <v>8.277477741241455</v>
+        <v>8.194710493087769</v>
       </c>
       <c r="J17" t="n">
-        <v>6.857656002044678</v>
+        <v>7.441612482070923</v>
       </c>
       <c r="K17" t="n">
-        <v>6.798717498779297</v>
+        <v>7.15086555480957</v>
       </c>
       <c r="L17" t="n">
-        <v>7.358692288398743</v>
+        <v>7.513050103187561</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>6.998184204101562</v>
+        <v>7.555346727371216</v>
       </c>
       <c r="C18" t="n">
-        <v>6.580749988555908</v>
+        <v>7.185305833816528</v>
       </c>
       <c r="D18" t="n">
-        <v>7.531338691711426</v>
+        <v>7.036670207977295</v>
       </c>
       <c r="E18" t="n">
-        <v>8.021556854248047</v>
+        <v>7.347379207611084</v>
       </c>
       <c r="F18" t="n">
-        <v>5.662099838256836</v>
+        <v>6.995802402496338</v>
       </c>
       <c r="G18" t="n">
-        <v>6.490981578826904</v>
+        <v>9.103818893432617</v>
       </c>
       <c r="H18" t="n">
-        <v>6.317447423934937</v>
+        <v>6.791824102401733</v>
       </c>
       <c r="I18" t="n">
-        <v>6.813649415969849</v>
+        <v>7.441604137420654</v>
       </c>
       <c r="J18" t="n">
-        <v>6.654031276702881</v>
+        <v>6.850160360336304</v>
       </c>
       <c r="K18" t="n">
-        <v>6.381792545318604</v>
+        <v>6.644728899002075</v>
       </c>
       <c r="L18" t="n">
-        <v>6.745183181762695</v>
+        <v>7.295264077186585</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>6.203226566314697</v>
+        <v>6.872101306915283</v>
       </c>
       <c r="C19" t="n">
-        <v>6.073508739471436</v>
+        <v>8.050067663192749</v>
       </c>
       <c r="D19" t="n">
-        <v>7.599688529968262</v>
+        <v>6.922017335891724</v>
       </c>
       <c r="E19" t="n">
-        <v>7.083471059799194</v>
+        <v>7.122971773147583</v>
       </c>
       <c r="F19" t="n">
-        <v>6.603171348571777</v>
+        <v>7.877496480941772</v>
       </c>
       <c r="G19" t="n">
-        <v>7.338845729827881</v>
+        <v>8.35428524017334</v>
       </c>
       <c r="H19" t="n">
-        <v>8.742218494415283</v>
+        <v>8.720813274383545</v>
       </c>
       <c r="I19" t="n">
-        <v>7.534286737442017</v>
+        <v>6.413331508636475</v>
       </c>
       <c r="J19" t="n">
-        <v>7.440059661865234</v>
+        <v>6.637732982635498</v>
       </c>
       <c r="K19" t="n">
-        <v>8.195133447647095</v>
+        <v>7.633117914199829</v>
       </c>
       <c r="L19" t="n">
-        <v>7.281361031532287</v>
+        <v>7.46039354801178</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>8.855995893478394</v>
+        <v>7.324416399002075</v>
       </c>
       <c r="C20" t="n">
-        <v>7.676649808883667</v>
+        <v>9.227997779846191</v>
       </c>
       <c r="D20" t="n">
-        <v>7.981643676757812</v>
+        <v>8.291892528533936</v>
       </c>
       <c r="E20" t="n">
-        <v>7.393912792205811</v>
+        <v>7.551323890686035</v>
       </c>
       <c r="F20" t="n">
-        <v>8.073429822921753</v>
+        <v>10.13607716560364</v>
       </c>
       <c r="G20" t="n">
-        <v>7.368243217468262</v>
+        <v>8.870889186859131</v>
       </c>
       <c r="H20" t="n">
-        <v>8.978673458099365</v>
+        <v>7.501008749008179</v>
       </c>
       <c r="I20" t="n">
-        <v>8.380656242370605</v>
+        <v>9.171104431152344</v>
       </c>
       <c r="J20" t="n">
-        <v>7.046180963516235</v>
+        <v>8.034119606018066</v>
       </c>
       <c r="K20" t="n">
-        <v>6.859663963317871</v>
+        <v>6.894039630889893</v>
       </c>
       <c r="L20" t="n">
-        <v>7.861504983901978</v>
+        <v>8.300286936759949</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>7.022737741470337</v>
+        <v>8.983105182647705</v>
       </c>
       <c r="C21" t="n">
-        <v>7.587796449661255</v>
+        <v>7.529889106750488</v>
       </c>
       <c r="D21" t="n">
-        <v>6.741472005844116</v>
+        <v>7.563659906387329</v>
       </c>
       <c r="E21" t="n">
-        <v>6.893068552017212</v>
+        <v>8.423542976379395</v>
       </c>
       <c r="F21" t="n">
-        <v>6.961954832077026</v>
+        <v>7.57915997505188</v>
       </c>
       <c r="G21" t="n">
-        <v>7.403746604919434</v>
+        <v>7.097412586212158</v>
       </c>
       <c r="H21" t="n">
-        <v>6.757901668548584</v>
+        <v>8.253489255905151</v>
       </c>
       <c r="I21" t="n">
-        <v>8.21773099899292</v>
+        <v>7.551251888275146</v>
       </c>
       <c r="J21" t="n">
-        <v>6.784369707107544</v>
+        <v>7.204609870910645</v>
       </c>
       <c r="K21" t="n">
-        <v>8.435067892074585</v>
+        <v>8.210067272186279</v>
       </c>
       <c r="L21" t="n">
-        <v>7.280584645271301</v>
+        <v>7.839618802070618</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>5.474257946014404</v>
+        <v>6.613155841827393</v>
       </c>
       <c r="C22" t="n">
-        <v>5.9281005859375</v>
+        <v>6.095958709716797</v>
       </c>
       <c r="D22" t="n">
-        <v>7.909932374954224</v>
+        <v>6.538824319839478</v>
       </c>
       <c r="E22" t="n">
-        <v>5.651318073272705</v>
+        <v>5.803195953369141</v>
       </c>
       <c r="F22" t="n">
-        <v>5.507217884063721</v>
+        <v>6.413344860076904</v>
       </c>
       <c r="G22" t="n">
-        <v>7.138929843902588</v>
+        <v>6.276500463485718</v>
       </c>
       <c r="H22" t="n">
-        <v>5.835885524749756</v>
+        <v>6.017657279968262</v>
       </c>
       <c r="I22" t="n">
-        <v>5.677757740020752</v>
+        <v>7.929314613342285</v>
       </c>
       <c r="J22" t="n">
-        <v>5.959553003311157</v>
+        <v>6.29645299911499</v>
       </c>
       <c r="K22" t="n">
-        <v>5.576002836227417</v>
+        <v>6.053554534912109</v>
       </c>
       <c r="L22" t="n">
-        <v>6.065895581245423</v>
+        <v>6.403795957565308</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>8.341572999954224</v>
+        <v>7.227574110031128</v>
       </c>
       <c r="C23" t="n">
-        <v>6.846558332443237</v>
+        <v>9.977564573287964</v>
       </c>
       <c r="D23" t="n">
-        <v>7.096435070037842</v>
+        <v>9.948162317276001</v>
       </c>
       <c r="E23" t="n">
-        <v>8.415574550628662</v>
+        <v>9.449902057647705</v>
       </c>
       <c r="F23" t="n">
-        <v>7.411121845245361</v>
+        <v>9.552660226821899</v>
       </c>
       <c r="G23" t="n">
-        <v>9.354686498641968</v>
+        <v>10.07033586502075</v>
       </c>
       <c r="H23" t="n">
-        <v>8.099866390228271</v>
+        <v>8.427666902542114</v>
       </c>
       <c r="I23" t="n">
-        <v>8.692855834960938</v>
+        <v>8.294889688491821</v>
       </c>
       <c r="J23" t="n">
-        <v>8.802581310272217</v>
+        <v>10.5914192199707</v>
       </c>
       <c r="K23" t="n">
-        <v>9.066424608230591</v>
+        <v>8.702281951904297</v>
       </c>
       <c r="L23" t="n">
-        <v>8.212767744064331</v>
+        <v>9.224245691299439</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>6.592721939086914</v>
+        <v>10.45533061027527</v>
       </c>
       <c r="C24" t="n">
-        <v>6.654574632644653</v>
+        <v>9.520223379135132</v>
       </c>
       <c r="D24" t="n">
-        <v>7.207674026489258</v>
+        <v>9.658354043960571</v>
       </c>
       <c r="E24" t="n">
-        <v>7.206624746322632</v>
+        <v>9.329710245132446</v>
       </c>
       <c r="F24" t="n">
-        <v>9.180125951766968</v>
+        <v>9.963592529296875</v>
       </c>
       <c r="G24" t="n">
-        <v>9.536216020584106</v>
+        <v>7.582189321517944</v>
       </c>
       <c r="H24" t="n">
-        <v>8.423576831817627</v>
+        <v>7.448558568954468</v>
       </c>
       <c r="I24" t="n">
-        <v>9.553663492202759</v>
+        <v>8.402576923370361</v>
       </c>
       <c r="J24" t="n">
-        <v>6.870492935180664</v>
+        <v>10.14965319633484</v>
       </c>
       <c r="K24" t="n">
-        <v>6.69846773147583</v>
+        <v>9.092337369918823</v>
       </c>
       <c r="L24" t="n">
-        <v>7.792413830757141</v>
+        <v>9.160252618789674</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>6.457079887390137</v>
+        <v>7.891387701034546</v>
       </c>
       <c r="C25" t="n">
-        <v>6.596708297729492</v>
+        <v>7.140289068222046</v>
       </c>
       <c r="D25" t="n">
-        <v>8.452968120574951</v>
+        <v>7.189688444137573</v>
       </c>
       <c r="E25" t="n">
-        <v>9.333713531494141</v>
+        <v>6.726354360580444</v>
       </c>
       <c r="F25" t="n">
-        <v>6.315442085266113</v>
+        <v>7.933253288269043</v>
       </c>
       <c r="G25" t="n">
-        <v>6.186246633529663</v>
+        <v>7.407109022140503</v>
       </c>
       <c r="H25" t="n">
-        <v>6.970395565032959</v>
+        <v>7.155255794525146</v>
       </c>
       <c r="I25" t="n">
-        <v>6.656545400619507</v>
+        <v>7.196674108505249</v>
       </c>
       <c r="J25" t="n">
-        <v>6.543824434280396</v>
+        <v>9.766574621200562</v>
       </c>
       <c r="K25" t="n">
-        <v>8.564662456512451</v>
+        <v>7.368226766586304</v>
       </c>
       <c r="L25" t="n">
-        <v>7.207758641242981</v>
+        <v>7.577481317520141</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>9.161148309707642</v>
+        <v>7.341779470443726</v>
       </c>
       <c r="C26" t="n">
-        <v>6.437621831893921</v>
+        <v>7.372195720672607</v>
       </c>
       <c r="D26" t="n">
-        <v>6.295486211776733</v>
+        <v>6.902900457382202</v>
       </c>
       <c r="E26" t="n">
-        <v>7.395173788070679</v>
+        <v>6.791173696517944</v>
       </c>
       <c r="F26" t="n">
-        <v>7.163250923156738</v>
+        <v>9.150694847106934</v>
       </c>
       <c r="G26" t="n">
-        <v>6.509946823120117</v>
+        <v>7.878906726837158</v>
       </c>
       <c r="H26" t="n">
-        <v>6.861037492752075</v>
+        <v>7.159748077392578</v>
       </c>
       <c r="I26" t="n">
-        <v>7.731834411621094</v>
+        <v>6.759272813796997</v>
       </c>
       <c r="J26" t="n">
-        <v>6.631135225296021</v>
+        <v>6.896124839782715</v>
       </c>
       <c r="K26" t="n">
-        <v>6.819639921188354</v>
+        <v>9.012022733688354</v>
       </c>
       <c r="L26" t="n">
-        <v>7.100627493858338</v>
+        <v>7.526481938362122</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>8.729300498962402</v>
+        <v>9.190555095672607</v>
       </c>
       <c r="C27" t="n">
-        <v>6.535843133926392</v>
+        <v>9.738689422607422</v>
       </c>
       <c r="D27" t="n">
-        <v>8.922830581665039</v>
+        <v>9.099301338195801</v>
       </c>
       <c r="E27" t="n">
-        <v>8.369697570800781</v>
+        <v>9.095315933227539</v>
       </c>
       <c r="F27" t="n">
-        <v>8.404582738876343</v>
+        <v>7.366725206375122</v>
       </c>
       <c r="G27" t="n">
-        <v>9.269383192062378</v>
+        <v>9.77574610710144</v>
       </c>
       <c r="H27" t="n">
-        <v>9.667459964752197</v>
+        <v>7.322846174240112</v>
       </c>
       <c r="I27" t="n">
-        <v>6.994690656661987</v>
+        <v>10.80847811698914</v>
       </c>
       <c r="J27" t="n">
-        <v>6.753838062286377</v>
+        <v>6.527853727340698</v>
       </c>
       <c r="K27" t="n">
-        <v>9.063908576965332</v>
+        <v>8.994099140167236</v>
       </c>
       <c r="L27" t="n">
-        <v>8.271153497695924</v>
+        <v>8.791961026191711</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>7.213630199432373</v>
+        <v>7.587677478790283</v>
       </c>
       <c r="C28" t="n">
-        <v>8.353740692138672</v>
+        <v>7.588694095611572</v>
       </c>
       <c r="D28" t="n">
-        <v>8.547744035720825</v>
+        <v>10.13767886161804</v>
       </c>
       <c r="E28" t="n">
-        <v>8.131773948669434</v>
+        <v>9.138226509094238</v>
       </c>
       <c r="F28" t="n">
-        <v>8.37964653968811</v>
+        <v>9.380120754241943</v>
       </c>
       <c r="G28" t="n">
-        <v>9.271450281143188</v>
+        <v>8.431668043136597</v>
       </c>
       <c r="H28" t="n">
-        <v>7.480453729629517</v>
+        <v>8.714281797409058</v>
       </c>
       <c r="I28" t="n">
-        <v>8.291881561279297</v>
+        <v>7.632553815841675</v>
       </c>
       <c r="J28" t="n">
-        <v>6.961291074752808</v>
+        <v>8.865377902984619</v>
       </c>
       <c r="K28" t="n">
-        <v>8.462438106536865</v>
+        <v>7.773224830627441</v>
       </c>
       <c r="L28" t="n">
-        <v>8.109405016899109</v>
+        <v>8.524950408935547</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>6.712430000305176</v>
+        <v>6.952781438827515</v>
       </c>
       <c r="C29" t="n">
-        <v>7.892396450042725</v>
+        <v>8.28838038444519</v>
       </c>
       <c r="D29" t="n">
-        <v>6.570306301116943</v>
+        <v>7.018130779266357</v>
       </c>
       <c r="E29" t="n">
-        <v>10.05541515350342</v>
+        <v>9.670895576477051</v>
       </c>
       <c r="F29" t="n">
-        <v>6.800707578659058</v>
+        <v>8.794060945510864</v>
       </c>
       <c r="G29" t="n">
-        <v>8.820469379425049</v>
+        <v>10.90972113609314</v>
       </c>
       <c r="H29" t="n">
-        <v>7.924305200576782</v>
+        <v>7.331850051879883</v>
       </c>
       <c r="I29" t="n">
-        <v>7.116385459899902</v>
+        <v>7.55776834487915</v>
       </c>
       <c r="J29" t="n">
-        <v>6.671037435531616</v>
+        <v>9.449889659881592</v>
       </c>
       <c r="K29" t="n">
-        <v>6.45207953453064</v>
+        <v>10.65485715866089</v>
       </c>
       <c r="L29" t="n">
-        <v>7.501553249359131</v>
+        <v>8.662833547592163</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>6.840599060058594</v>
+        <v>7.469940185546875</v>
       </c>
       <c r="C30" t="n">
-        <v>7.118385076522827</v>
+        <v>7.663455486297607</v>
       </c>
       <c r="D30" t="n">
-        <v>6.737340688705444</v>
+        <v>9.29033899307251</v>
       </c>
       <c r="E30" t="n">
-        <v>6.814646482467651</v>
+        <v>7.439048767089844</v>
       </c>
       <c r="F30" t="n">
-        <v>6.451085329055786</v>
+        <v>8.80058765411377</v>
       </c>
       <c r="G30" t="n">
-        <v>8.100370645523071</v>
+        <v>10.09576392173767</v>
       </c>
       <c r="H30" t="n">
-        <v>6.789682865142822</v>
+        <v>7.401143312454224</v>
       </c>
       <c r="I30" t="n">
-        <v>7.321855068206787</v>
+        <v>8.505816221237183</v>
       </c>
       <c r="J30" t="n">
-        <v>6.896917104721069</v>
+        <v>7.611618757247925</v>
       </c>
       <c r="K30" t="n">
-        <v>6.836573839187622</v>
+        <v>7.891889810562134</v>
       </c>
       <c r="L30" t="n">
-        <v>6.990745615959168</v>
+        <v>8.216960310935974</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>6.532861948013306</v>
+        <v>6.698944807052612</v>
       </c>
       <c r="C31" t="n">
-        <v>6.990210771560669</v>
+        <v>7.597831249237061</v>
       </c>
       <c r="D31" t="n">
-        <v>6.666527032852173</v>
+        <v>6.878621816635132</v>
       </c>
       <c r="E31" t="n">
-        <v>6.638083696365356</v>
+        <v>9.751147508621216</v>
       </c>
       <c r="F31" t="n">
-        <v>6.631119728088379</v>
+        <v>8.872552156448364</v>
       </c>
       <c r="G31" t="n">
-        <v>9.271905899047852</v>
+        <v>6.840547561645508</v>
       </c>
       <c r="H31" t="n">
-        <v>9.079999446868896</v>
+        <v>9.067909002304077</v>
       </c>
       <c r="I31" t="n">
-        <v>9.244667530059814</v>
+        <v>6.914888858795166</v>
       </c>
       <c r="J31" t="n">
-        <v>7.447603225708008</v>
+        <v>9.56464409828186</v>
       </c>
       <c r="K31" t="n">
-        <v>6.802691221237183</v>
+        <v>8.469428300857544</v>
       </c>
       <c r="L31" t="n">
-        <v>7.530567049980164</v>
+        <v>8.065651535987854</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>6.427666902542114</v>
+        <v>6.471503257751465</v>
       </c>
       <c r="C32" t="n">
-        <v>8.094397068023682</v>
+        <v>7.194645404815674</v>
       </c>
       <c r="D32" t="n">
-        <v>10.08882713317871</v>
+        <v>7.065004348754883</v>
       </c>
       <c r="E32" t="n">
-        <v>9.152279376983643</v>
+        <v>7.102416515350342</v>
       </c>
       <c r="F32" t="n">
-        <v>6.860023021697998</v>
+        <v>7.026108026504517</v>
       </c>
       <c r="G32" t="n">
-        <v>6.190224885940552</v>
+        <v>6.689445734024048</v>
       </c>
       <c r="H32" t="n">
-        <v>8.764205932617188</v>
+        <v>8.775684118270874</v>
       </c>
       <c r="I32" t="n">
-        <v>6.261591196060181</v>
+        <v>7.204660177230835</v>
       </c>
       <c r="J32" t="n">
-        <v>6.147834300994873</v>
+        <v>6.567769765853882</v>
       </c>
       <c r="K32" t="n">
-        <v>6.688478946685791</v>
+        <v>9.281837224960327</v>
       </c>
       <c r="L32" t="n">
-        <v>7.467552876472473</v>
+        <v>7.337907457351685</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>7.140300035476685</v>
+        <v>8.441529750823975</v>
       </c>
       <c r="C33" t="n">
-        <v>7.122369289398193</v>
+        <v>7.610599994659424</v>
       </c>
       <c r="D33" t="n">
-        <v>7.109380960464478</v>
+        <v>7.800099611282349</v>
       </c>
       <c r="E33" t="n">
-        <v>6.414696455001831</v>
+        <v>7.098403692245483</v>
       </c>
       <c r="F33" t="n">
-        <v>6.017662048339844</v>
+        <v>7.831058263778687</v>
       </c>
       <c r="G33" t="n">
-        <v>6.426647186279297</v>
+        <v>6.847543478012085</v>
       </c>
       <c r="H33" t="n">
-        <v>6.649354219436646</v>
+        <v>7.466461658477783</v>
       </c>
       <c r="I33" t="n">
-        <v>6.970920085906982</v>
+        <v>7.620550632476807</v>
       </c>
       <c r="J33" t="n">
-        <v>6.935442447662354</v>
+        <v>6.98570728302002</v>
       </c>
       <c r="K33" t="n">
-        <v>6.551474332809448</v>
+        <v>7.54378867149353</v>
       </c>
       <c r="L33" t="n">
-        <v>6.733824706077575</v>
+        <v>7.524574303627015</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>7.057058095932007</v>
+        <v>6.673980712890625</v>
       </c>
       <c r="C34" t="n">
-        <v>7.214638948440552</v>
+        <v>7.588148355484009</v>
       </c>
       <c r="D34" t="n">
-        <v>7.980669736862183</v>
+        <v>6.019679546356201</v>
       </c>
       <c r="E34" t="n">
-        <v>5.815231800079346</v>
+        <v>6.292499303817749</v>
       </c>
       <c r="F34" t="n">
-        <v>7.34682559967041</v>
+        <v>6.602159261703491</v>
       </c>
       <c r="G34" t="n">
-        <v>5.925404787063599</v>
+        <v>6.232102870941162</v>
       </c>
       <c r="H34" t="n">
-        <v>7.182685852050781</v>
+        <v>8.600097894668579</v>
       </c>
       <c r="I34" t="n">
-        <v>6.165802240371704</v>
+        <v>7.470927715301514</v>
       </c>
       <c r="J34" t="n">
-        <v>6.05808162689209</v>
+        <v>7.926792621612549</v>
       </c>
       <c r="K34" t="n">
-        <v>7.773691177368164</v>
+        <v>6.932833433151245</v>
       </c>
       <c r="L34" t="n">
-        <v>6.852008986473083</v>
+        <v>7.033922171592712</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>8.76874828338623</v>
+        <v>9.387097835540771</v>
       </c>
       <c r="C35" t="n">
-        <v>7.087968349456787</v>
+        <v>7.729789733886719</v>
       </c>
       <c r="D35" t="n">
-        <v>8.358803749084473</v>
+        <v>7.709841728210449</v>
       </c>
       <c r="E35" t="n">
-        <v>7.112423181533813</v>
+        <v>7.916313648223877</v>
       </c>
       <c r="F35" t="n">
-        <v>7.375712871551514</v>
+        <v>9.44092845916748</v>
       </c>
       <c r="G35" t="n">
-        <v>8.596108436584473</v>
+        <v>8.196117877960205</v>
       </c>
       <c r="H35" t="n">
-        <v>9.287882089614868</v>
+        <v>9.150172233581543</v>
       </c>
       <c r="I35" t="n">
-        <v>7.277448177337646</v>
+        <v>9.990605592727661</v>
       </c>
       <c r="J35" t="n">
-        <v>7.212631940841675</v>
+        <v>7.046048641204834</v>
       </c>
       <c r="K35" t="n">
-        <v>7.369278192520142</v>
+        <v>7.833059072494507</v>
       </c>
       <c r="L35" t="n">
-        <v>7.844700527191162</v>
+        <v>8.439997482299805</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>9.00906229019165</v>
+        <v>8.538749217987061</v>
       </c>
       <c r="C36" t="n">
-        <v>10.10574102401733</v>
+        <v>8.066934585571289</v>
       </c>
       <c r="D36" t="n">
-        <v>8.46644926071167</v>
+        <v>8.062481164932251</v>
       </c>
       <c r="E36" t="n">
-        <v>7.328875780105591</v>
+        <v>10.19302082061768</v>
       </c>
       <c r="F36" t="n">
-        <v>7.613599061965942</v>
+        <v>9.111290693283081</v>
       </c>
       <c r="G36" t="n">
-        <v>7.630566835403442</v>
+        <v>7.787153005599976</v>
       </c>
       <c r="H36" t="n">
-        <v>7.825445413589478</v>
+        <v>8.058446168899536</v>
       </c>
       <c r="I36" t="n">
-        <v>7.785762786865234</v>
+        <v>10.18507814407349</v>
       </c>
       <c r="J36" t="n">
-        <v>8.340799331665039</v>
+        <v>7.89484691619873</v>
       </c>
       <c r="K36" t="n">
-        <v>7.523943662643433</v>
+        <v>8.557191848754883</v>
       </c>
       <c r="L36" t="n">
-        <v>8.163024544715881</v>
+        <v>8.645519256591797</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>6.21184515953064</v>
+        <v>6.902896642684937</v>
       </c>
       <c r="C37" t="n">
-        <v>5.665759563446045</v>
+        <v>6.653029441833496</v>
       </c>
       <c r="D37" t="n">
-        <v>6.087678670883179</v>
+        <v>6.543374061584473</v>
       </c>
       <c r="E37" t="n">
-        <v>6.151511669158936</v>
+        <v>6.682956457138062</v>
       </c>
       <c r="F37" t="n">
-        <v>6.352958679199219</v>
+        <v>6.079995155334473</v>
       </c>
       <c r="G37" t="n">
-        <v>6.04577374458313</v>
+        <v>8.05846095085144</v>
       </c>
       <c r="H37" t="n">
-        <v>8.273504018783569</v>
+        <v>6.260555744171143</v>
       </c>
       <c r="I37" t="n">
-        <v>6.549992084503174</v>
+        <v>6.666001558303833</v>
       </c>
       <c r="J37" t="n">
-        <v>5.99892783164978</v>
+        <v>7.038569450378418</v>
       </c>
       <c r="K37" t="n">
-        <v>5.716665983200073</v>
+        <v>6.900413990020752</v>
       </c>
       <c r="L37" t="n">
-        <v>6.305461740493774</v>
+        <v>6.778625345230102</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>6.764565229415894</v>
+        <v>6.930819511413574</v>
       </c>
       <c r="C38" t="n">
-        <v>6.76325798034668</v>
+        <v>9.917233467102051</v>
       </c>
       <c r="D38" t="n">
-        <v>7.252019643783569</v>
+        <v>6.709434032440186</v>
       </c>
       <c r="E38" t="n">
-        <v>6.51293420791626</v>
+        <v>6.705394506454468</v>
       </c>
       <c r="F38" t="n">
-        <v>6.38123893737793</v>
+        <v>6.713403463363647</v>
       </c>
       <c r="G38" t="n">
-        <v>6.606193542480469</v>
+        <v>7.427091836929321</v>
       </c>
       <c r="H38" t="n">
-        <v>6.632598876953125</v>
+        <v>6.503918647766113</v>
       </c>
       <c r="I38" t="n">
-        <v>6.111441612243652</v>
+        <v>6.980709791183472</v>
       </c>
       <c r="J38" t="n">
-        <v>8.41655969619751</v>
+        <v>6.992172002792358</v>
       </c>
       <c r="K38" t="n">
-        <v>6.326921463012695</v>
+        <v>9.240803956985474</v>
       </c>
       <c r="L38" t="n">
-        <v>6.776773118972779</v>
+        <v>7.412098121643067</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>6.260054588317871</v>
+        <v>6.523503541946411</v>
       </c>
       <c r="C39" t="n">
-        <v>6.752300024032593</v>
+        <v>7.050217390060425</v>
       </c>
       <c r="D39" t="n">
-        <v>8.321310043334961</v>
+        <v>6.874111413955688</v>
       </c>
       <c r="E39" t="n">
-        <v>6.628151416778564</v>
+        <v>6.637240409851074</v>
       </c>
       <c r="F39" t="n">
-        <v>7.779196500778198</v>
+        <v>7.066280841827393</v>
       </c>
       <c r="G39" t="n">
-        <v>6.335358858108521</v>
+        <v>6.940654039382935</v>
       </c>
       <c r="H39" t="n">
-        <v>6.464029312133789</v>
+        <v>8.633580923080444</v>
       </c>
       <c r="I39" t="n">
-        <v>6.261049270629883</v>
+        <v>6.858668804168701</v>
       </c>
       <c r="J39" t="n">
-        <v>6.114945411682129</v>
+        <v>8.229580163955688</v>
       </c>
       <c r="K39" t="n">
-        <v>7.964714288711548</v>
+        <v>6.57188606262207</v>
       </c>
       <c r="L39" t="n">
-        <v>6.888110971450805</v>
+        <v>7.138572359085083</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>6.189257860183716</v>
+        <v>7.270102977752686</v>
       </c>
       <c r="C40" t="n">
-        <v>6.417635440826416</v>
+        <v>6.90453028678894</v>
       </c>
       <c r="D40" t="n">
-        <v>6.933849573135376</v>
+        <v>6.884567260742188</v>
       </c>
       <c r="E40" t="n">
-        <v>6.648089408874512</v>
+        <v>7.932862043380737</v>
       </c>
       <c r="F40" t="n">
-        <v>6.779719114303589</v>
+        <v>9.022535562515259</v>
       </c>
       <c r="G40" t="n">
-        <v>6.232149124145508</v>
+        <v>7.522947311401367</v>
       </c>
       <c r="H40" t="n">
-        <v>6.439626216888428</v>
+        <v>10.19944190979004</v>
       </c>
       <c r="I40" t="n">
-        <v>6.921860218048096</v>
+        <v>8.732780694961548</v>
       </c>
       <c r="J40" t="n">
-        <v>6.809676647186279</v>
+        <v>7.15489387512207</v>
       </c>
       <c r="K40" t="n">
-        <v>8.536755323410034</v>
+        <v>6.532490491867065</v>
       </c>
       <c r="L40" t="n">
-        <v>6.790861892700195</v>
+        <v>7.81571524143219</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>8.564197778701782</v>
+        <v>9.622950077056885</v>
       </c>
       <c r="C41" t="n">
-        <v>7.036110401153564</v>
+        <v>7.708442449569702</v>
       </c>
       <c r="D41" t="n">
-        <v>7.196680545806885</v>
+        <v>7.757321357727051</v>
       </c>
       <c r="E41" t="n">
-        <v>7.401148080825806</v>
+        <v>8.071489095687866</v>
       </c>
       <c r="F41" t="n">
-        <v>7.469980716705322</v>
+        <v>7.496000289916992</v>
       </c>
       <c r="G41" t="n">
-        <v>7.093441009521484</v>
+        <v>10.48770260810852</v>
       </c>
       <c r="H41" t="n">
-        <v>7.330798864364624</v>
+        <v>10.09822559356689</v>
       </c>
       <c r="I41" t="n">
-        <v>8.725327491760254</v>
+        <v>8.876903057098389</v>
       </c>
       <c r="J41" t="n">
-        <v>6.940818548202515</v>
+        <v>8.368727207183838</v>
       </c>
       <c r="K41" t="n">
-        <v>7.273013830184937</v>
+        <v>8.343803405761719</v>
       </c>
       <c r="L41" t="n">
-        <v>7.503151726722717</v>
+        <v>8.683156514167786</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>5.253730535507202</v>
+        <v>6.592838525772095</v>
       </c>
       <c r="C42" t="n">
-        <v>5.443355321884155</v>
+        <v>5.854292631149292</v>
       </c>
       <c r="D42" t="n">
-        <v>5.358557939529419</v>
+        <v>5.670226573944092</v>
       </c>
       <c r="E42" t="n">
-        <v>7.209253549575806</v>
+        <v>5.65975546836853</v>
       </c>
       <c r="F42" t="n">
-        <v>5.477248430252075</v>
+        <v>6.489841222763062</v>
       </c>
       <c r="G42" t="n">
-        <v>5.827842950820923</v>
+        <v>7.807089567184448</v>
       </c>
       <c r="H42" t="n">
-        <v>4.978049516677856</v>
+        <v>6.078017473220825</v>
       </c>
       <c r="I42" t="n">
-        <v>5.244356155395508</v>
+        <v>5.735869646072388</v>
       </c>
       <c r="J42" t="n">
-        <v>5.298584222793579</v>
+        <v>5.550863981246948</v>
       </c>
       <c r="K42" t="n">
-        <v>5.009966373443604</v>
+        <v>6.175772905349731</v>
       </c>
       <c r="L42" t="n">
-        <v>5.510094499588012</v>
+        <v>6.161456799507141</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>6.74601149559021</v>
+        <v>6.652044534683228</v>
       </c>
       <c r="C43" t="n">
-        <v>6.600815773010254</v>
+        <v>8.917765140533447</v>
       </c>
       <c r="D43" t="n">
-        <v>7.428685188293457</v>
+        <v>8.118812561035156</v>
       </c>
       <c r="E43" t="n">
-        <v>7.066203832626343</v>
+        <v>7.181193828582764</v>
       </c>
       <c r="F43" t="n">
-        <v>6.278663158416748</v>
+        <v>8.363188505172729</v>
       </c>
       <c r="G43" t="n">
-        <v>6.023216724395752</v>
+        <v>8.482359409332275</v>
       </c>
       <c r="H43" t="n">
-        <v>7.013127565383911</v>
+        <v>6.317480802536011</v>
       </c>
       <c r="I43" t="n">
-        <v>6.087992906570435</v>
+        <v>8.293846607208252</v>
       </c>
       <c r="J43" t="n">
-        <v>7.449042797088623</v>
+        <v>6.827636003494263</v>
       </c>
       <c r="K43" t="n">
-        <v>5.906510829925537</v>
+        <v>6.868008136749268</v>
       </c>
       <c r="L43" t="n">
-        <v>6.660027027130127</v>
+        <v>7.60223355293274</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>7.022130250930786</v>
+        <v>9.160661220550537</v>
       </c>
       <c r="C44" t="n">
-        <v>6.582244873046875</v>
+        <v>7.923314571380615</v>
       </c>
       <c r="D44" t="n">
-        <v>6.746351957321167</v>
+        <v>7.264472723007202</v>
       </c>
       <c r="E44" t="n">
-        <v>6.753791093826294</v>
+        <v>7.157779216766357</v>
       </c>
       <c r="F44" t="n">
-        <v>6.657058238983154</v>
+        <v>7.340157032012939</v>
       </c>
       <c r="G44" t="n">
-        <v>8.985180616378784</v>
+        <v>8.005177736282349</v>
       </c>
       <c r="H44" t="n">
-        <v>8.964668750762939</v>
+        <v>6.807278871536255</v>
       </c>
       <c r="I44" t="n">
-        <v>7.610648155212402</v>
+        <v>8.077995777130127</v>
       </c>
       <c r="J44" t="n">
-        <v>7.909365892410278</v>
+        <v>7.104647636413574</v>
       </c>
       <c r="K44" t="n">
-        <v>6.912883281707764</v>
+        <v>6.522898435592651</v>
       </c>
       <c r="L44" t="n">
-        <v>7.414432311058045</v>
+        <v>7.53643832206726</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>8.558696746826172</v>
+        <v>8.235598802566528</v>
       </c>
       <c r="C45" t="n">
-        <v>6.660552978515625</v>
+        <v>9.25241756439209</v>
       </c>
       <c r="D45" t="n">
-        <v>7.697908163070679</v>
+        <v>9.39707088470459</v>
       </c>
       <c r="E45" t="n">
-        <v>9.576135635375977</v>
+        <v>8.680852651596069</v>
       </c>
       <c r="F45" t="n">
-        <v>7.221639156341553</v>
+        <v>8.892808675765991</v>
       </c>
       <c r="G45" t="n">
-        <v>7.407176971435547</v>
+        <v>9.288821458816528</v>
       </c>
       <c r="H45" t="n">
-        <v>8.642011404037476</v>
+        <v>7.517370462417603</v>
       </c>
       <c r="I45" t="n">
-        <v>7.154790878295898</v>
+        <v>10.11669850349426</v>
       </c>
       <c r="J45" t="n">
-        <v>9.000084161758423</v>
+        <v>9.670330762863159</v>
       </c>
       <c r="K45" t="n">
-        <v>7.530322790145874</v>
+        <v>10.53693675994873</v>
       </c>
       <c r="L45" t="n">
-        <v>7.944931888580323</v>
+        <v>9.158890652656556</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>7.391663074493408</v>
+        <v>8.831485271453857</v>
       </c>
       <c r="C46" t="n">
-        <v>8.163238286972046</v>
+        <v>7.163246870040894</v>
       </c>
       <c r="D46" t="n">
-        <v>7.494491100311279</v>
+        <v>9.084347248077393</v>
       </c>
       <c r="E46" t="n">
-        <v>6.750308275222778</v>
+        <v>8.287413120269775</v>
       </c>
       <c r="F46" t="n">
-        <v>9.537218809127808</v>
+        <v>9.260355710983276</v>
       </c>
       <c r="G46" t="n">
-        <v>8.591152667999268</v>
+        <v>8.636978626251221</v>
       </c>
       <c r="H46" t="n">
-        <v>7.880125045776367</v>
+        <v>10.10509824752808</v>
       </c>
       <c r="I46" t="n">
-        <v>6.944341421127319</v>
+        <v>7.616578340530396</v>
       </c>
       <c r="J46" t="n">
-        <v>8.141745805740356</v>
+        <v>7.569245100021362</v>
       </c>
       <c r="K46" t="n">
-        <v>7.754793643951416</v>
+        <v>8.566163063049316</v>
       </c>
       <c r="L46" t="n">
-        <v>7.864907813072205</v>
+        <v>8.512091159820557</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>7.397192239761353</v>
+        <v>7.580666065216064</v>
       </c>
       <c r="C47" t="n">
-        <v>8.292391300201416</v>
+        <v>10.11771535873413</v>
       </c>
       <c r="D47" t="n">
-        <v>7.464994430541992</v>
+        <v>8.921777486801147</v>
       </c>
       <c r="E47" t="n">
-        <v>7.133861303329468</v>
+        <v>9.723721027374268</v>
       </c>
       <c r="F47" t="n">
-        <v>7.386670589447021</v>
+        <v>9.479341268539429</v>
       </c>
       <c r="G47" t="n">
-        <v>7.127393960952759</v>
+        <v>7.589149475097656</v>
       </c>
       <c r="H47" t="n">
-        <v>8.586131811141968</v>
+        <v>9.809007406234741</v>
       </c>
       <c r="I47" t="n">
-        <v>7.432082414627075</v>
+        <v>8.153715848922729</v>
       </c>
       <c r="J47" t="n">
-        <v>8.265468597412109</v>
+        <v>8.842598438262939</v>
       </c>
       <c r="K47" t="n">
-        <v>8.266954660415649</v>
+        <v>9.844909906387329</v>
       </c>
       <c r="L47" t="n">
-        <v>7.735314130783081</v>
+        <v>9.006260228157043</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>10.13469338417053</v>
+        <v>6.915878295898438</v>
       </c>
       <c r="C48" t="n">
-        <v>7.869962930679321</v>
+        <v>6.488955736160278</v>
       </c>
       <c r="D48" t="n">
-        <v>6.102959632873535</v>
+        <v>8.532758235931396</v>
       </c>
       <c r="E48" t="n">
-        <v>8.154244661331177</v>
+        <v>6.974701166152954</v>
       </c>
       <c r="F48" t="n">
-        <v>6.170782327651978</v>
+        <v>8.719260215759277</v>
       </c>
       <c r="G48" t="n">
-        <v>7.956767082214355</v>
+        <v>5.907438278198242</v>
       </c>
       <c r="H48" t="n">
-        <v>7.035065174102783</v>
+        <v>7.27497410774231</v>
       </c>
       <c r="I48" t="n">
-        <v>6.43163013458252</v>
+        <v>7.690912961959839</v>
       </c>
       <c r="J48" t="n">
-        <v>6.375793933868408</v>
+        <v>8.120815277099609</v>
       </c>
       <c r="K48" t="n">
-        <v>8.590660095214844</v>
+        <v>6.439577579498291</v>
       </c>
       <c r="L48" t="n">
-        <v>7.482255935668945</v>
+        <v>7.306527185440063</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>9.023144483566284</v>
+        <v>7.369201898574829</v>
       </c>
       <c r="C49" t="n">
-        <v>8.135411262512207</v>
+        <v>7.553252696990967</v>
       </c>
       <c r="D49" t="n">
-        <v>7.070004224777222</v>
+        <v>7.511377573013306</v>
       </c>
       <c r="E49" t="n">
-        <v>7.737804174423218</v>
+        <v>8.5651695728302</v>
       </c>
       <c r="F49" t="n">
-        <v>9.545196294784546</v>
+        <v>7.294381856918335</v>
       </c>
       <c r="G49" t="n">
-        <v>6.900952577590942</v>
+        <v>7.489413738250732</v>
       </c>
       <c r="H49" t="n">
-        <v>6.762801647186279</v>
+        <v>9.479328632354736</v>
       </c>
       <c r="I49" t="n">
-        <v>7.246552467346191</v>
+        <v>7.653480052947998</v>
       </c>
       <c r="J49" t="n">
-        <v>7.629565477371216</v>
+        <v>8.050482988357544</v>
       </c>
       <c r="K49" t="n">
-        <v>7.640556812286377</v>
+        <v>7.914337635040283</v>
       </c>
       <c r="L49" t="n">
-        <v>7.769198942184448</v>
+        <v>7.888042664527893</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>7.077962160110474</v>
+        <v>8.514799833297729</v>
       </c>
       <c r="C50" t="n">
-        <v>8.793647527694702</v>
+        <v>8.907804727554321</v>
       </c>
       <c r="D50" t="n">
-        <v>7.390137672424316</v>
+        <v>9.843419313430786</v>
       </c>
       <c r="E50" t="n">
-        <v>9.127745628356934</v>
+        <v>9.77742600440979</v>
       </c>
       <c r="F50" t="n">
-        <v>7.555887937545776</v>
+        <v>7.644091606140137</v>
       </c>
       <c r="G50" t="n">
-        <v>7.64012885093689</v>
+        <v>9.020511150360107</v>
       </c>
       <c r="H50" t="n">
-        <v>9.390582323074341</v>
+        <v>11.17787957191467</v>
       </c>
       <c r="I50" t="n">
-        <v>7.036692380905151</v>
+        <v>6.885071754455566</v>
       </c>
       <c r="J50" t="n">
-        <v>7.423300981521606</v>
+        <v>7.395771980285645</v>
       </c>
       <c r="K50" t="n">
-        <v>6.771432876586914</v>
+        <v>10.74553966522217</v>
       </c>
       <c r="L50" t="n">
-        <v>7.82075183391571</v>
+        <v>8.991231560707092</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>7.447613000869751</v>
+        <v>7.615188598632812</v>
       </c>
       <c r="C51" t="n">
-        <v>8.065512657165527</v>
+        <v>8.272462844848633</v>
       </c>
       <c r="D51" t="n">
-        <v>6.991314649581909</v>
+        <v>8.544796466827393</v>
       </c>
       <c r="E51" t="n">
-        <v>7.198301553726196</v>
+        <v>7.377283096313477</v>
       </c>
       <c r="F51" t="n">
-        <v>6.751476526260376</v>
+        <v>7.527890920639038</v>
       </c>
       <c r="G51" t="n">
-        <v>8.094946146011353</v>
+        <v>9.316738128662109</v>
       </c>
       <c r="H51" t="n">
-        <v>6.979843616485596</v>
+        <v>7.401175022125244</v>
       </c>
       <c r="I51" t="n">
-        <v>7.862547397613525</v>
+        <v>7.768243312835693</v>
       </c>
       <c r="J51" t="n">
-        <v>7.097061395645142</v>
+        <v>8.385132789611816</v>
       </c>
       <c r="K51" t="n">
-        <v>6.823242425918579</v>
+        <v>8.782613039016724</v>
       </c>
       <c r="L51" t="n">
-        <v>7.331185936927795</v>
+        <v>8.099152421951294</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7.320380711555481</v>
+        <v>7.744611797332763</v>
       </c>
       <c r="C52" t="n">
-        <v>7.045639886856079</v>
+        <v>7.886473922729492</v>
       </c>
       <c r="D52" t="n">
-        <v>7.242583985328674</v>
+        <v>7.767311329841614</v>
       </c>
       <c r="E52" t="n">
-        <v>7.214865460395813</v>
+        <v>7.817659420967102</v>
       </c>
       <c r="F52" t="n">
-        <v>7.161251187324524</v>
+        <v>7.813824963569641</v>
       </c>
       <c r="G52" t="n">
-        <v>7.299981026649475</v>
+        <v>8.10957311630249</v>
       </c>
       <c r="H52" t="n">
-        <v>7.418465752601623</v>
+        <v>7.79108416557312</v>
       </c>
       <c r="I52" t="n">
-        <v>7.178407216072083</v>
+        <v>7.812529673576355</v>
       </c>
       <c r="J52" t="n">
-        <v>7.122917876243592</v>
+        <v>7.673039255142212</v>
       </c>
       <c r="K52" t="n">
-        <v>7.254294290542602</v>
+        <v>7.962453966140747</v>
       </c>
       <c r="L52" t="n">
-        <v>7.225878739356996</v>
+        <v>7.837856161117554</v>
       </c>
     </row>
   </sheetData>
